--- a/grupos/2ASV - Estadisticos 20222.xlsx
+++ b/grupos/2ASV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="145">
   <si>
     <t>Materia</t>
   </si>
@@ -192,16 +192,16 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Saucedo Rivalcoba Graciela</t>
-  </si>
-  <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
     <t>Sánchez Sánchez Miguel</t>
@@ -951,7 +951,7 @@
         <v>5</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>6</v>
@@ -1005,7 +1005,7 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -1028,7 +1028,7 @@
         <v>7</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>7</v>
@@ -1082,7 +1082,7 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -1105,7 +1105,7 @@
         <v>7</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -1159,7 +1159,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1182,7 +1182,7 @@
         <v>5</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>8</v>
@@ -1236,7 +1236,7 @@
         <v>5</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1259,7 +1259,7 @@
         <v>5</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G8">
         <v>7</v>
@@ -1313,7 +1313,7 @@
         <v>5</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1336,7 +1336,7 @@
         <v>7</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>6</v>
@@ -1390,7 +1390,7 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1413,7 +1413,7 @@
         <v>7</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>8</v>
@@ -1467,7 +1467,7 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1490,7 +1490,7 @@
         <v>5</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G11">
         <v>7</v>
@@ -1544,7 +1544,7 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1567,7 +1567,7 @@
         <v>5</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G12">
         <v>6</v>
@@ -1621,7 +1621,7 @@
         <v>5</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1644,7 +1644,7 @@
         <v>6</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>9</v>
@@ -1698,7 +1698,7 @@
         <v>6</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1721,7 +1721,7 @@
         <v>7</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>8</v>
@@ -1775,7 +1775,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1798,7 +1798,7 @@
         <v>6</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>8</v>
@@ -1852,7 +1852,7 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1875,7 +1875,7 @@
         <v>5</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G16">
         <v>6</v>
@@ -1929,7 +1929,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -1952,7 +1952,7 @@
         <v>5</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G17">
         <v>6</v>
@@ -2006,7 +2006,7 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -2029,7 +2029,7 @@
         <v>6</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G18">
         <v>7</v>
@@ -2083,7 +2083,7 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -2106,7 +2106,7 @@
         <v>6</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>6</v>
@@ -2160,7 +2160,7 @@
         <v>6</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2183,7 +2183,7 @@
         <v>5</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -2237,7 +2237,7 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2260,7 +2260,7 @@
         <v>6</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>7</v>
@@ -2314,7 +2314,7 @@
         <v>6</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2337,7 +2337,7 @@
         <v>7</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G22">
         <v>7</v>
@@ -2391,7 +2391,7 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2414,7 +2414,7 @@
         <v>5</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G23">
         <v>6</v>
@@ -2468,7 +2468,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>6</v>
@@ -2491,7 +2491,7 @@
         <v>5</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G24">
         <v>6</v>
@@ -2545,7 +2545,7 @@
         <v>5</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2568,7 +2568,7 @@
         <v>7</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G25">
         <v>6</v>
@@ -2622,7 +2622,7 @@
         <v>7</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>6</v>
@@ -2645,7 +2645,7 @@
         <v>8</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>10</v>
@@ -2699,7 +2699,7 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2722,7 +2722,7 @@
         <v>6</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G27">
         <v>10</v>
@@ -2776,7 +2776,7 @@
         <v>6</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -2799,7 +2799,7 @@
         <v>5</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>6</v>
@@ -2853,7 +2853,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -2876,7 +2876,7 @@
         <v>9</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G29">
         <v>10</v>
@@ -2930,7 +2930,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y29">
         <v>10</v>
@@ -2953,7 +2953,7 @@
         <v>5</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>6</v>
@@ -3007,7 +3007,7 @@
         <v>5</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y30">
         <v>6</v>
@@ -3030,7 +3030,7 @@
         <v>6</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G31">
         <v>6</v>
@@ -3084,7 +3084,7 @@
         <v>6</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>6</v>
@@ -3107,7 +3107,7 @@
         <v>5</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G32">
         <v>5</v>
@@ -3161,7 +3161,7 @@
         <v>5</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>5</v>
@@ -3184,7 +3184,7 @@
         <v>7</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -3238,7 +3238,7 @@
         <v>7</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y33">
         <v>5</v>
@@ -3261,7 +3261,7 @@
         <v>5</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G34">
         <v>6</v>
@@ -3315,7 +3315,7 @@
         <v>5</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>6</v>
@@ -3338,7 +3338,7 @@
         <v>6</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G35">
         <v>7</v>
@@ -3392,7 +3392,7 @@
         <v>6</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y35">
         <v>7</v>
@@ -3415,7 +3415,7 @@
         <v>6</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G36">
         <v>6</v>
@@ -3469,7 +3469,7 @@
         <v>6</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -3602,7 +3602,7 @@
         <v>94.3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -3661,7 +3661,7 @@
         <v>94.3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -3720,7 +3720,7 @@
         <v>94.3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>100</v>
@@ -3779,7 +3779,7 @@
         <v>94.3</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -3838,7 +3838,7 @@
         <v>94.3</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G8">
         <v>100</v>
@@ -3897,7 +3897,7 @@
         <v>94.3</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -3956,7 +3956,7 @@
         <v>94.3</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>100</v>
@@ -4015,7 +4015,7 @@
         <v>94.3</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -4074,7 +4074,7 @@
         <v>94.3</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -4133,7 +4133,7 @@
         <v>94.3</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>100</v>
@@ -4192,7 +4192,7 @@
         <v>94.3</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G14">
         <v>90</v>
@@ -4251,7 +4251,7 @@
         <v>94.3</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -4310,7 +4310,7 @@
         <v>94.3</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G16">
         <v>100</v>
@@ -4369,7 +4369,7 @@
         <v>94.3</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G17">
         <v>100</v>
@@ -4428,7 +4428,7 @@
         <v>94.3</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G18">
         <v>100</v>
@@ -4487,7 +4487,7 @@
         <v>94.3</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G19">
         <v>100</v>
@@ -4546,7 +4546,7 @@
         <v>94.3</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G20">
         <v>90</v>
@@ -4605,7 +4605,7 @@
         <v>94.3</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21">
         <v>100</v>
@@ -4664,7 +4664,7 @@
         <v>94.3</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G22">
         <v>100</v>
@@ -4723,7 +4723,7 @@
         <v>94.3</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G23">
         <v>100</v>
@@ -4782,7 +4782,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24">
         <v>100</v>
@@ -4841,7 +4841,7 @@
         <v>94.3</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G25">
         <v>100</v>
@@ -4900,7 +4900,7 @@
         <v>94.3</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26">
         <v>100</v>
@@ -4959,7 +4959,7 @@
         <v>94.3</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27">
         <v>100</v>
@@ -5018,7 +5018,7 @@
         <v>94.3</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G28">
         <v>100</v>
@@ -5077,7 +5077,7 @@
         <v>94.3</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G29">
         <v>100</v>
@@ -5136,7 +5136,7 @@
         <v>94.3</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G30">
         <v>100</v>
@@ -5195,7 +5195,7 @@
         <v>94.3</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G31">
         <v>95</v>
@@ -5254,7 +5254,7 @@
         <v>85.7</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G32">
         <v>100</v>
@@ -5313,7 +5313,7 @@
         <v>94.3</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G33">
         <v>95</v>
@@ -5372,7 +5372,7 @@
         <v>94.3</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34">
         <v>95</v>
@@ -5431,7 +5431,7 @@
         <v>94.3</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G35">
         <v>100</v>
@@ -5490,7 +5490,7 @@
         <v>94.3</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G36">
         <v>100</v>
@@ -5584,7 +5584,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
@@ -5613,7 +5613,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -5622,27 +5622,30 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>57.58</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>42.42</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -5651,19 +5654,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>57.58</v>
+        <v>90.91</v>
       </c>
       <c r="G4">
-        <v>42.42</v>
+        <v>9.09</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5674,7 +5677,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -5683,19 +5686,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>90.91</v>
+        <v>93.94</v>
       </c>
       <c r="G5">
-        <v>9.09</v>
+        <v>6.06</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5709,7 +5712,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>33</v>
@@ -5775,7 +5778,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5816,7 +5819,7 @@
         <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>57</v>
@@ -5824,39 +5827,39 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920290</v>
+        <v>22330051920291</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920291</v>
+        <v>22330051920293</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>57</v>
@@ -5864,39 +5867,39 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920291</v>
+        <v>22330051920294</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920293</v>
+        <v>22330051920412</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>57</v>
@@ -5904,39 +5907,39 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920293</v>
+        <v>22330051920295</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920294</v>
+        <v>22330051920360</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>57</v>
@@ -5944,39 +5947,39 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920294</v>
+        <v>22330051920297</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920412</v>
+        <v>22330051920415</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>57</v>
@@ -5984,39 +5987,39 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920412</v>
+        <v>22330051920298</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920295</v>
+        <v>22330051920300</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>57</v>
@@ -6024,39 +6027,39 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920295</v>
+        <v>22330051920301</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920360</v>
+        <v>22330051920302</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
         <v>57</v>
@@ -6064,39 +6067,39 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920360</v>
+        <v>22330051920303</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920297</v>
+        <v>22330051920304</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
         <v>57</v>
@@ -6104,39 +6107,39 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920297</v>
+        <v>22330051920305</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920415</v>
+        <v>22330051920417</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
         <v>57</v>
@@ -6144,39 +6147,39 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>22330051920415</v>
+        <v>22330051920306</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>22330051920298</v>
+        <v>22330051920307</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
         <v>57</v>
@@ -6184,39 +6187,39 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>22330051920298</v>
+        <v>22330051920419</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E21" t="s">
         <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>22330051920300</v>
+        <v>22330051920309</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F22" t="s">
         <v>57</v>
@@ -6224,39 +6227,39 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>22330051920300</v>
+        <v>22330051920308</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="E23" t="s">
         <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>22330051920301</v>
+        <v>22330051920310</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
         <v>57</v>
@@ -6264,39 +6267,36 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>22330051920301</v>
+        <v>22330051920311</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E25" t="s">
         <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>22330051920302</v>
+        <v>22330051920312</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
         <v>57</v>
@@ -6304,39 +6304,39 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>22330051920302</v>
+        <v>22330051920364</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="E27" t="s">
         <v>6</v>
       </c>
       <c r="F27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>22330051920303</v>
+        <v>22330051920313</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F28" t="s">
         <v>57</v>
@@ -6344,39 +6344,39 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>22330051920303</v>
+        <v>22330051920370</v>
       </c>
       <c r="B29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" t="s">
         <v>77</v>
       </c>
-      <c r="C29" t="s">
-        <v>71</v>
-      </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="E29" t="s">
         <v>6</v>
       </c>
       <c r="F29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>22330051920304</v>
+        <v>22330051920418</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F30" t="s">
         <v>57</v>
@@ -6384,39 +6384,39 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>22330051920304</v>
+        <v>22330051920397</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="E31" t="s">
         <v>6</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>22330051920305</v>
+        <v>22330051920408</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F32" t="s">
         <v>57</v>
@@ -6424,696 +6424,42 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>22330051920305</v>
+        <v>22330051920314</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E33" t="s">
         <v>6</v>
       </c>
       <c r="F33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>22330051920417</v>
+        <v>22330051920315</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="D34" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F34" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>22330051920417</v>
-      </c>
-      <c r="B35" t="s">
-        <v>78</v>
-      </c>
-      <c r="C35" t="s">
-        <v>92</v>
-      </c>
-      <c r="D35" t="s">
-        <v>130</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>22330051920306</v>
-      </c>
-      <c r="B36" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" t="s">
-        <v>105</v>
-      </c>
-      <c r="D36" t="s">
-        <v>131</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>22330051920306</v>
-      </c>
-      <c r="B37" t="s">
-        <v>79</v>
-      </c>
-      <c r="C37" t="s">
-        <v>105</v>
-      </c>
-      <c r="D37" t="s">
-        <v>131</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>22330051920307</v>
-      </c>
-      <c r="B38" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" t="s">
-        <v>106</v>
-      </c>
-      <c r="D38" t="s">
-        <v>132</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>22330051920307</v>
-      </c>
-      <c r="B39" t="s">
-        <v>80</v>
-      </c>
-      <c r="C39" t="s">
-        <v>106</v>
-      </c>
-      <c r="D39" t="s">
-        <v>132</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>22330051920419</v>
-      </c>
-      <c r="B40" t="s">
-        <v>81</v>
-      </c>
-      <c r="C40" t="s">
-        <v>104</v>
-      </c>
-      <c r="D40" t="s">
-        <v>133</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>22330051920419</v>
-      </c>
-      <c r="B41" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" t="s">
-        <v>104</v>
-      </c>
-      <c r="D41" t="s">
-        <v>133</v>
-      </c>
-      <c r="E41" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>22330051920309</v>
-      </c>
-      <c r="B42" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" t="s">
-        <v>105</v>
-      </c>
-      <c r="D42" t="s">
-        <v>134</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>22330051920309</v>
-      </c>
-      <c r="B43" t="s">
-        <v>82</v>
-      </c>
-      <c r="C43" t="s">
-        <v>105</v>
-      </c>
-      <c r="D43" t="s">
-        <v>134</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>22330051920308</v>
-      </c>
-      <c r="B44" t="s">
-        <v>83</v>
-      </c>
-      <c r="C44" t="s">
-        <v>77</v>
-      </c>
-      <c r="D44" t="s">
-        <v>90</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>22330051920308</v>
-      </c>
-      <c r="B45" t="s">
-        <v>83</v>
-      </c>
-      <c r="C45" t="s">
-        <v>77</v>
-      </c>
-      <c r="D45" t="s">
-        <v>90</v>
-      </c>
-      <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>22330051920310</v>
-      </c>
-      <c r="B46" t="s">
-        <v>84</v>
-      </c>
-      <c r="C46" t="s">
-        <v>107</v>
-      </c>
-      <c r="D46" t="s">
-        <v>135</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>22330051920310</v>
-      </c>
-      <c r="B47" t="s">
-        <v>84</v>
-      </c>
-      <c r="C47" t="s">
-        <v>107</v>
-      </c>
-      <c r="D47" t="s">
-        <v>135</v>
-      </c>
-      <c r="E47" t="s">
-        <v>6</v>
-      </c>
-      <c r="F47" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>22330051920311</v>
-      </c>
-      <c r="B48" t="s">
-        <v>85</v>
-      </c>
-      <c r="D48" t="s">
-        <v>136</v>
-      </c>
-      <c r="E48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>22330051920311</v>
-      </c>
-      <c r="B49" t="s">
-        <v>85</v>
-      </c>
-      <c r="D49" t="s">
-        <v>136</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>22330051920312</v>
-      </c>
-      <c r="B50" t="s">
-        <v>86</v>
-      </c>
-      <c r="C50" t="s">
-        <v>108</v>
-      </c>
-      <c r="D50" t="s">
-        <v>137</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>22330051920312</v>
-      </c>
-      <c r="B51" t="s">
-        <v>86</v>
-      </c>
-      <c r="C51" t="s">
-        <v>108</v>
-      </c>
-      <c r="D51" t="s">
-        <v>137</v>
-      </c>
-      <c r="E51" t="s">
-        <v>6</v>
-      </c>
-      <c r="F51" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>22330051920364</v>
-      </c>
-      <c r="B52" t="s">
-        <v>87</v>
-      </c>
-      <c r="C52" t="s">
-        <v>109</v>
-      </c>
-      <c r="D52" t="s">
-        <v>138</v>
-      </c>
-      <c r="E52" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>22330051920364</v>
-      </c>
-      <c r="B53" t="s">
-        <v>87</v>
-      </c>
-      <c r="C53" t="s">
-        <v>109</v>
-      </c>
-      <c r="D53" t="s">
-        <v>138</v>
-      </c>
-      <c r="E53" t="s">
-        <v>6</v>
-      </c>
-      <c r="F53" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>22330051920313</v>
-      </c>
-      <c r="B54" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" t="s">
-        <v>110</v>
-      </c>
-      <c r="D54" t="s">
-        <v>139</v>
-      </c>
-      <c r="E54" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>22330051920313</v>
-      </c>
-      <c r="B55" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" t="s">
-        <v>110</v>
-      </c>
-      <c r="D55" t="s">
-        <v>139</v>
-      </c>
-      <c r="E55" t="s">
-        <v>6</v>
-      </c>
-      <c r="F55" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>22330051920370</v>
-      </c>
-      <c r="B56" t="s">
-        <v>89</v>
-      </c>
-      <c r="C56" t="s">
-        <v>77</v>
-      </c>
-      <c r="D56" t="s">
-        <v>140</v>
-      </c>
-      <c r="E56" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>22330051920370</v>
-      </c>
-      <c r="B57" t="s">
-        <v>89</v>
-      </c>
-      <c r="C57" t="s">
-        <v>77</v>
-      </c>
-      <c r="D57" t="s">
-        <v>140</v>
-      </c>
-      <c r="E57" t="s">
-        <v>6</v>
-      </c>
-      <c r="F57" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>22330051920418</v>
-      </c>
-      <c r="B58" t="s">
-        <v>90</v>
-      </c>
-      <c r="C58" t="s">
-        <v>79</v>
-      </c>
-      <c r="D58" t="s">
-        <v>141</v>
-      </c>
-      <c r="E58" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>22330051920418</v>
-      </c>
-      <c r="B59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C59" t="s">
-        <v>79</v>
-      </c>
-      <c r="D59" t="s">
-        <v>141</v>
-      </c>
-      <c r="E59" t="s">
-        <v>6</v>
-      </c>
-      <c r="F59" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>22330051920397</v>
-      </c>
-      <c r="B60" t="s">
-        <v>91</v>
-      </c>
-      <c r="C60" t="s">
-        <v>89</v>
-      </c>
-      <c r="D60" t="s">
-        <v>142</v>
-      </c>
-      <c r="E60" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>22330051920397</v>
-      </c>
-      <c r="B61" t="s">
-        <v>91</v>
-      </c>
-      <c r="C61" t="s">
-        <v>89</v>
-      </c>
-      <c r="D61" t="s">
-        <v>142</v>
-      </c>
-      <c r="E61" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>22330051920408</v>
-      </c>
-      <c r="B62" t="s">
-        <v>92</v>
-      </c>
-      <c r="C62" t="s">
-        <v>111</v>
-      </c>
-      <c r="D62" t="s">
-        <v>133</v>
-      </c>
-      <c r="E62" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>22330051920408</v>
-      </c>
-      <c r="B63" t="s">
-        <v>92</v>
-      </c>
-      <c r="C63" t="s">
-        <v>111</v>
-      </c>
-      <c r="D63" t="s">
-        <v>133</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>22330051920314</v>
-      </c>
-      <c r="B64" t="s">
-        <v>93</v>
-      </c>
-      <c r="C64" t="s">
-        <v>112</v>
-      </c>
-      <c r="D64" t="s">
-        <v>143</v>
-      </c>
-      <c r="E64" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>22330051920314</v>
-      </c>
-      <c r="B65" t="s">
-        <v>93</v>
-      </c>
-      <c r="C65" t="s">
-        <v>112</v>
-      </c>
-      <c r="D65" t="s">
-        <v>143</v>
-      </c>
-      <c r="E65" t="s">
-        <v>6</v>
-      </c>
-      <c r="F65" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>22330051920315</v>
-      </c>
-      <c r="B66" t="s">
-        <v>94</v>
-      </c>
-      <c r="C66" t="s">
-        <v>113</v>
-      </c>
-      <c r="D66" t="s">
-        <v>144</v>
-      </c>
-      <c r="E66" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>22330051920315</v>
-      </c>
-      <c r="B67" t="s">
-        <v>94</v>
-      </c>
-      <c r="C67" t="s">
-        <v>113</v>
-      </c>
-      <c r="D67" t="s">
-        <v>144</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -7161,7 +6507,7 @@
         <v>114</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -7178,7 +6524,7 @@
         <v>115</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7195,7 +6541,7 @@
         <v>116</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7212,7 +6558,7 @@
         <v>117</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -7229,7 +6575,7 @@
         <v>118</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -7246,7 +6592,7 @@
         <v>119</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -7263,7 +6609,7 @@
         <v>120</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -7280,7 +6626,7 @@
         <v>121</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7297,7 +6643,7 @@
         <v>122</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -7314,7 +6660,7 @@
         <v>123</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -7331,7 +6677,7 @@
         <v>124</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -7348,7 +6694,7 @@
         <v>125</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -7365,7 +6711,7 @@
         <v>126</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -7382,7 +6728,7 @@
         <v>127</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -7399,7 +6745,7 @@
         <v>128</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -7416,7 +6762,7 @@
         <v>129</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -7433,7 +6779,7 @@
         <v>130</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -7450,7 +6796,7 @@
         <v>131</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -7467,7 +6813,7 @@
         <v>132</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -7484,7 +6830,7 @@
         <v>133</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -7501,7 +6847,7 @@
         <v>134</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -7518,7 +6864,7 @@
         <v>90</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -7535,7 +6881,7 @@
         <v>135</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -7549,7 +6895,7 @@
         <v>136</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -7566,7 +6912,7 @@
         <v>137</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -7583,7 +6929,7 @@
         <v>138</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -7600,7 +6946,7 @@
         <v>139</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -7617,7 +6963,7 @@
         <v>140</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -7634,7 +6980,7 @@
         <v>141</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -7651,7 +6997,7 @@
         <v>142</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -7668,7 +7014,7 @@
         <v>133</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -7685,7 +7031,7 @@
         <v>143</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -7702,7 +7048,7 @@
         <v>144</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7712,7 +7058,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7744,22 +7090,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920291</v>
+        <v>22330051920290</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -7767,45 +7113,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920291</v>
+        <v>22330051920290</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920293</v>
+        <v>22330051920291</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -7813,45 +7159,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920293</v>
+        <v>22330051920291</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920295</v>
+        <v>22330051920294</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -7859,45 +7205,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920295</v>
+        <v>22330051920294</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920360</v>
+        <v>22330051920412</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -7905,45 +7251,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920360</v>
+        <v>22330051920412</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920415</v>
+        <v>22330051920297</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -7951,45 +7297,45 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920415</v>
+        <v>22330051920297</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920300</v>
+        <v>22330051920298</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -7997,45 +7343,45 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920300</v>
+        <v>22330051920298</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920301</v>
+        <v>22330051920302</v>
       </c>
       <c r="B14" t="s">
         <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -8043,45 +7389,45 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920301</v>
+        <v>22330051920302</v>
       </c>
       <c r="B15" t="s">
         <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920304</v>
+        <v>22330051920303</v>
       </c>
       <c r="B16" t="s">
         <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -8089,45 +7435,45 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920304</v>
+        <v>22330051920303</v>
       </c>
       <c r="B17" t="s">
         <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920305</v>
+        <v>22330051920419</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
         <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E18" t="s">
         <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G18">
         <v>-1</v>
@@ -8135,45 +7481,45 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920305</v>
+        <v>22330051920419</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
         <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920306</v>
+        <v>22330051920308</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G20">
         <v>-1</v>
@@ -8181,45 +7527,45 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920306</v>
+        <v>22330051920308</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920307</v>
+        <v>22330051920312</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G22">
         <v>-1</v>
@@ -8227,45 +7573,45 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920307</v>
+        <v>22330051920312</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920309</v>
+        <v>22330051920364</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E24" t="s">
         <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G24">
         <v>-1</v>
@@ -8273,45 +7619,45 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920309</v>
+        <v>22330051920364</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920310</v>
+        <v>22330051920397</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E26" t="s">
         <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G26">
         <v>-1</v>
@@ -8319,42 +7665,45 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920310</v>
+        <v>22330051920397</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920311</v>
+        <v>22330051920293</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>68</v>
+      </c>
+      <c r="C28" t="s">
+        <v>97</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="E28" t="s">
         <v>6</v>
       </c>
       <c r="F28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G28">
         <v>-1</v>
@@ -8362,16 +7711,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920311</v>
+        <v>22330051920295</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>71</v>
+      </c>
+      <c r="C29" t="s">
+        <v>99</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
         <v>57</v>
@@ -8382,22 +7734,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920313</v>
+        <v>22330051920360</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s">
         <v>6</v>
       </c>
       <c r="F30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G30">
         <v>-1</v>
@@ -8405,19 +7757,19 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920313</v>
+        <v>22330051920415</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D31" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F31" t="s">
         <v>57</v>
@@ -8428,22 +7780,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920370</v>
+        <v>22330051920300</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s">
         <v>6</v>
       </c>
       <c r="F32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G32">
         <v>-1</v>
@@ -8451,19 +7803,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920370</v>
+        <v>22330051920301</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="D33" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E33" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F33" t="s">
         <v>57</v>
@@ -8474,22 +7826,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>22330051920314</v>
+        <v>22330051920304</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="E34" t="s">
         <v>6</v>
       </c>
       <c r="F34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G34">
         <v>-1</v>
@@ -8497,19 +7849,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>22330051920314</v>
+        <v>22330051920305</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C35" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D35" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F35" t="s">
         <v>57</v>
@@ -8520,22 +7872,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>22330051920315</v>
+        <v>22330051920306</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="C36" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E36" t="s">
         <v>6</v>
       </c>
       <c r="F36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G36">
         <v>-1</v>
@@ -8543,24 +7895,182 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>22330051920315</v>
+        <v>22330051920307</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C37" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="E37" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F37" t="s">
         <v>57</v>
       </c>
       <c r="G37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>22330051920309</v>
+      </c>
+      <c r="B38" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" t="s">
+        <v>105</v>
+      </c>
+      <c r="D38" t="s">
+        <v>134</v>
+      </c>
+      <c r="E38" t="s">
+        <v>6</v>
+      </c>
+      <c r="F38" t="s">
+        <v>57</v>
+      </c>
+      <c r="G38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>22330051920310</v>
+      </c>
+      <c r="B39" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" t="s">
+        <v>107</v>
+      </c>
+      <c r="D39" t="s">
+        <v>135</v>
+      </c>
+      <c r="E39" t="s">
+        <v>6</v>
+      </c>
+      <c r="F39" t="s">
+        <v>57</v>
+      </c>
+      <c r="G39">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>22330051920311</v>
+      </c>
+      <c r="B40" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" t="s">
+        <v>136</v>
+      </c>
+      <c r="E40" t="s">
+        <v>6</v>
+      </c>
+      <c r="F40" t="s">
+        <v>57</v>
+      </c>
+      <c r="G40">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>22330051920313</v>
+      </c>
+      <c r="B41" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" t="s">
+        <v>110</v>
+      </c>
+      <c r="D41" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" t="s">
+        <v>6</v>
+      </c>
+      <c r="F41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G41">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>22330051920370</v>
+      </c>
+      <c r="B42" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" t="s">
+        <v>140</v>
+      </c>
+      <c r="E42" t="s">
+        <v>6</v>
+      </c>
+      <c r="F42" t="s">
+        <v>57</v>
+      </c>
+      <c r="G42">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>22330051920314</v>
+      </c>
+      <c r="B43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" t="s">
+        <v>112</v>
+      </c>
+      <c r="D43" t="s">
+        <v>143</v>
+      </c>
+      <c r="E43" t="s">
+        <v>6</v>
+      </c>
+      <c r="F43" t="s">
+        <v>57</v>
+      </c>
+      <c r="G43">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>22330051920315</v>
+      </c>
+      <c r="B44" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" t="s">
+        <v>113</v>
+      </c>
+      <c r="D44" t="s">
+        <v>144</v>
+      </c>
+      <c r="E44" t="s">
+        <v>6</v>
+      </c>
+      <c r="F44" t="s">
+        <v>57</v>
+      </c>
+      <c r="G44">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ASV - Estadisticos 20222.xlsx
+++ b/grupos/2ASV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="145">
   <si>
     <t>Materia</t>
   </si>
@@ -942,7 +942,7 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -996,7 +996,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -1073,7 +1073,7 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>6</v>
@@ -1096,7 +1096,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>9</v>
@@ -1150,7 +1150,7 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -1173,7 +1173,7 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -1227,7 +1227,7 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1250,7 +1250,7 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>9</v>
@@ -1304,7 +1304,7 @@
         <v>7</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1327,7 +1327,7 @@
         <v>9</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -1381,7 +1381,7 @@
         <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1404,7 +1404,7 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>7</v>
@@ -1458,7 +1458,7 @@
         <v>9</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -1481,7 +1481,7 @@
         <v>8</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>9</v>
@@ -1535,7 +1535,7 @@
         <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1558,7 +1558,7 @@
         <v>9</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -1612,7 +1612,7 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>6</v>
@@ -1635,7 +1635,7 @@
         <v>10</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <v>9</v>
@@ -1689,7 +1689,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -1712,7 +1712,7 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -1766,7 +1766,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>7</v>
@@ -1789,7 +1789,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D15">
         <v>6</v>
@@ -1843,7 +1843,7 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -1866,7 +1866,7 @@
         <v>9</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>6</v>
@@ -1920,7 +1920,7 @@
         <v>9</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>6</v>
@@ -1943,7 +1943,7 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D17">
         <v>7</v>
@@ -1997,7 +1997,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>7</v>
@@ -2020,7 +2020,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D18">
         <v>6</v>
@@ -2074,7 +2074,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>6</v>
@@ -2097,7 +2097,7 @@
         <v>8</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D19">
         <v>6</v>
@@ -2151,7 +2151,7 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>6</v>
@@ -2174,7 +2174,7 @@
         <v>8</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>8</v>
@@ -2228,7 +2228,7 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -2251,7 +2251,7 @@
         <v>9</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -2305,7 +2305,7 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>6</v>
@@ -2328,7 +2328,7 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <v>7</v>
@@ -2382,7 +2382,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>7</v>
@@ -2405,7 +2405,7 @@
         <v>8</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D23">
         <v>7</v>
@@ -2459,7 +2459,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -2482,7 +2482,7 @@
         <v>8</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>7</v>
@@ -2536,7 +2536,7 @@
         <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -2559,7 +2559,7 @@
         <v>10</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D25">
         <v>8</v>
@@ -2613,7 +2613,7 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>8</v>
@@ -2636,7 +2636,7 @@
         <v>10</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D26">
         <v>9</v>
@@ -2690,7 +2690,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -2713,7 +2713,7 @@
         <v>8</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -2767,7 +2767,7 @@
         <v>8</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>6</v>
@@ -2790,7 +2790,7 @@
         <v>9</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -2844,7 +2844,7 @@
         <v>9</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>6</v>
@@ -2867,7 +2867,7 @@
         <v>10</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D29">
         <v>9</v>
@@ -2921,7 +2921,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2944,7 +2944,7 @@
         <v>8</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>7</v>
@@ -2998,7 +2998,7 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>7</v>
@@ -3021,7 +3021,7 @@
         <v>8</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D31">
         <v>9</v>
@@ -3075,7 +3075,7 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3098,7 +3098,7 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D32">
         <v>6</v>
@@ -3152,7 +3152,7 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V32">
         <v>6</v>
@@ -3175,7 +3175,7 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D33">
         <v>6</v>
@@ -3229,7 +3229,7 @@
         <v>8</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V33">
         <v>6</v>
@@ -3252,7 +3252,7 @@
         <v>8</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D34">
         <v>9</v>
@@ -3306,7 +3306,7 @@
         <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>9</v>
@@ -3329,7 +3329,7 @@
         <v>9</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D35">
         <v>7</v>
@@ -3383,7 +3383,7 @@
         <v>9</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V35">
         <v>7</v>
@@ -3406,7 +3406,7 @@
         <v>10</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D36">
         <v>9</v>
@@ -3460,7 +3460,7 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V36">
         <v>9</v>
@@ -3593,7 +3593,7 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -3652,7 +3652,7 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -3711,7 +3711,7 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D6">
         <v>100</v>
@@ -3770,7 +3770,7 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="D7">
         <v>100</v>
@@ -3829,7 +3829,7 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D8">
         <v>100</v>
@@ -3888,7 +3888,7 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D9">
         <v>100</v>
@@ -3947,7 +3947,7 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D10">
         <v>100</v>
@@ -4006,7 +4006,7 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -4065,7 +4065,7 @@
         <v>100</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D12">
         <v>100</v>
@@ -4124,7 +4124,7 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -4183,7 +4183,7 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D14">
         <v>100</v>
@@ -4242,7 +4242,7 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D15">
         <v>100</v>
@@ -4301,7 +4301,7 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D16">
         <v>100</v>
@@ -4360,7 +4360,7 @@
         <v>100</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D17">
         <v>100</v>
@@ -4419,7 +4419,7 @@
         <v>100</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="D18">
         <v>100</v>
@@ -4478,7 +4478,7 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D19">
         <v>100</v>
@@ -4537,7 +4537,7 @@
         <v>100</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D20">
         <v>100</v>
@@ -4596,7 +4596,7 @@
         <v>100</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D21">
         <v>100</v>
@@ -4655,7 +4655,7 @@
         <v>100</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>100</v>
@@ -4714,7 +4714,7 @@
         <v>100</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>100</v>
@@ -4773,7 +4773,7 @@
         <v>100</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D24">
         <v>100</v>
@@ -4832,7 +4832,7 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -4891,7 +4891,7 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D26">
         <v>100</v>
@@ -4950,7 +4950,7 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D27">
         <v>100</v>
@@ -5009,7 +5009,7 @@
         <v>100</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D28">
         <v>100</v>
@@ -5068,7 +5068,7 @@
         <v>100</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D29">
         <v>100</v>
@@ -5127,7 +5127,7 @@
         <v>100</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D30">
         <v>100</v>
@@ -5186,7 +5186,7 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D31">
         <v>100</v>
@@ -5245,7 +5245,7 @@
         <v>100</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D32">
         <v>100</v>
@@ -5304,7 +5304,7 @@
         <v>100</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D33">
         <v>100</v>
@@ -5363,7 +5363,7 @@
         <v>100</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D34">
         <v>100</v>
@@ -5422,7 +5422,7 @@
         <v>100</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="D35">
         <v>100</v>
@@ -5481,7 +5481,7 @@
         <v>100</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>100</v>
@@ -5593,22 +5593,25 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>54.55</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>45.45</v>
+      </c>
+      <c r="H2">
+        <v>6.1</v>
       </c>
       <c r="I2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5778,7 +5781,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5803,663 +5806,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920290</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920291</v>
-      </c>
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920293</v>
-      </c>
-      <c r="B4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920294</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920412</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920295</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920360</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920297</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920415</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920298</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" t="s">
-        <v>123</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920300</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920301</v>
-      </c>
-      <c r="B13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920302</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" t="s">
-        <v>126</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920303</v>
-      </c>
-      <c r="B15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" t="s">
-        <v>127</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920304</v>
-      </c>
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" t="s">
-        <v>128</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920305</v>
-      </c>
-      <c r="B17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" t="s">
-        <v>129</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920417</v>
-      </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920306</v>
-      </c>
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" t="s">
-        <v>131</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920307</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>106</v>
-      </c>
-      <c r="D20" t="s">
-        <v>132</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920419</v>
-      </c>
-      <c r="B21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" t="s">
-        <v>104</v>
-      </c>
-      <c r="D21" t="s">
-        <v>133</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920309</v>
-      </c>
-      <c r="B22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" t="s">
-        <v>134</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920308</v>
-      </c>
-      <c r="B23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920310</v>
-      </c>
-      <c r="B24" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" t="s">
-        <v>107</v>
-      </c>
-      <c r="D24" t="s">
-        <v>135</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920311</v>
-      </c>
-      <c r="B25" t="s">
-        <v>85</v>
-      </c>
-      <c r="D25" t="s">
-        <v>136</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920312</v>
-      </c>
-      <c r="B26" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" t="s">
-        <v>137</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920364</v>
-      </c>
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" t="s">
-        <v>138</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920313</v>
-      </c>
-      <c r="B28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" t="s">
-        <v>110</v>
-      </c>
-      <c r="D28" t="s">
-        <v>139</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920370</v>
-      </c>
-      <c r="B29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" t="s">
-        <v>77</v>
-      </c>
-      <c r="D29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920418</v>
-      </c>
-      <c r="B30" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" t="s">
-        <v>79</v>
-      </c>
-      <c r="D30" t="s">
-        <v>141</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920397</v>
-      </c>
-      <c r="B31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>89</v>
-      </c>
-      <c r="D31" t="s">
-        <v>142</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>22330051920408</v>
-      </c>
-      <c r="B32" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" t="s">
-        <v>111</v>
-      </c>
-      <c r="D32" t="s">
-        <v>133</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>22330051920314</v>
-      </c>
-      <c r="B33" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" t="s">
-        <v>143</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>22330051920315</v>
-      </c>
-      <c r="B34" t="s">
-        <v>94</v>
-      </c>
-      <c r="C34" t="s">
-        <v>113</v>
-      </c>
-      <c r="D34" t="s">
-        <v>144</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -6507,7 +5853,7 @@
         <v>114</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6524,7 +5870,7 @@
         <v>115</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6541,7 +5887,7 @@
         <v>116</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6558,7 +5904,7 @@
         <v>117</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -6575,7 +5921,7 @@
         <v>118</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6592,7 +5938,7 @@
         <v>119</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6609,7 +5955,7 @@
         <v>120</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6626,7 +5972,7 @@
         <v>121</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6643,7 +5989,7 @@
         <v>122</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6660,7 +6006,7 @@
         <v>123</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6677,7 +6023,7 @@
         <v>124</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6694,7 +6040,7 @@
         <v>125</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6711,7 +6057,7 @@
         <v>126</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6728,7 +6074,7 @@
         <v>127</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6745,7 +6091,7 @@
         <v>128</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6762,7 +6108,7 @@
         <v>129</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6779,7 +6125,7 @@
         <v>130</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -6796,7 +6142,7 @@
         <v>131</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -6813,7 +6159,7 @@
         <v>132</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6830,7 +6176,7 @@
         <v>133</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -6847,7 +6193,7 @@
         <v>134</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -6864,7 +6210,7 @@
         <v>90</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -6881,7 +6227,7 @@
         <v>135</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -6895,7 +6241,7 @@
         <v>136</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -6912,7 +6258,7 @@
         <v>137</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -6929,7 +6275,7 @@
         <v>138</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -6946,7 +6292,7 @@
         <v>139</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -6963,7 +6309,7 @@
         <v>140</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -6980,7 +6326,7 @@
         <v>141</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -6997,7 +6343,7 @@
         <v>142</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -7014,7 +6360,7 @@
         <v>133</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -7031,7 +6377,7 @@
         <v>143</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -7048,7 +6394,7 @@
         <v>144</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7058,7 +6404,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7090,16 +6436,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920290</v>
+        <v>22330051920294</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -7108,21 +6454,21 @@
         <v>57</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920290</v>
+        <v>22330051920294</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7136,16 +6482,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920291</v>
+        <v>22330051920412</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -7154,27 +6500,27 @@
         <v>57</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920291</v>
+        <v>22330051920412</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7182,16 +6528,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920294</v>
+        <v>22330051920297</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -7200,21 +6546,21 @@
         <v>57</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920294</v>
+        <v>22330051920297</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -7228,16 +6574,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920412</v>
+        <v>22330051920298</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -7246,21 +6592,21 @@
         <v>57</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920412</v>
+        <v>22330051920298</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -7274,16 +6620,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920297</v>
+        <v>22330051920302</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -7292,21 +6638,21 @@
         <v>57</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920297</v>
+        <v>22330051920302</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -7320,16 +6666,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920298</v>
+        <v>22330051920303</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -7338,21 +6684,21 @@
         <v>57</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920298</v>
+        <v>22330051920303</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -7366,45 +6712,45 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920302</v>
+        <v>22330051920417</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
         <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920302</v>
+        <v>22330051920417</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
         <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7412,16 +6758,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920303</v>
+        <v>22330051920419</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -7430,21 +6776,21 @@
         <v>57</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920303</v>
+        <v>22330051920419</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -7458,16 +6804,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920419</v>
+        <v>22330051920308</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>90</v>
       </c>
       <c r="E18" t="s">
         <v>6</v>
@@ -7476,21 +6822,21 @@
         <v>57</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920419</v>
+        <v>22330051920308</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>133</v>
+        <v>90</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -7504,16 +6850,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920308</v>
+        <v>22330051920312</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
@@ -7522,21 +6868,21 @@
         <v>57</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920308</v>
+        <v>22330051920312</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -7550,16 +6896,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920312</v>
+        <v>22330051920397</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
@@ -7568,21 +6914,21 @@
         <v>57</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920312</v>
+        <v>22330051920397</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -7596,45 +6942,45 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920364</v>
+        <v>22330051920290</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920364</v>
+        <v>22330051920291</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -7642,16 +6988,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920397</v>
+        <v>22330051920307</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="E26" t="s">
         <v>6</v>
@@ -7660,27 +7006,24 @@
         <v>57</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920397</v>
+        <v>22330051920311</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -7688,39 +7031,39 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920293</v>
+        <v>22330051920364</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920295</v>
+        <v>22330051920370</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="E29" t="s">
         <v>6</v>
@@ -7729,349 +7072,7 @@
         <v>57</v>
       </c>
       <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>22330051920360</v>
-      </c>
-      <c r="B30" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" t="s">
-        <v>120</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>22330051920415</v>
-      </c>
-      <c r="B31" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" t="s">
-        <v>102</v>
-      </c>
-      <c r="D31" t="s">
-        <v>122</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>57</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>22330051920300</v>
-      </c>
-      <c r="B32" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32" t="s">
-        <v>124</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>57</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>22330051920301</v>
-      </c>
-      <c r="B33" t="s">
-        <v>76</v>
-      </c>
-      <c r="C33" t="s">
-        <v>103</v>
-      </c>
-      <c r="D33" t="s">
-        <v>125</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>57</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>22330051920304</v>
-      </c>
-      <c r="B34" t="s">
-        <v>77</v>
-      </c>
-      <c r="C34" t="s">
-        <v>77</v>
-      </c>
-      <c r="D34" t="s">
-        <v>128</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>57</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>22330051920305</v>
-      </c>
-      <c r="B35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" t="s">
-        <v>104</v>
-      </c>
-      <c r="D35" t="s">
-        <v>129</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>57</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>22330051920306</v>
-      </c>
-      <c r="B36" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" t="s">
-        <v>105</v>
-      </c>
-      <c r="D36" t="s">
-        <v>131</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>57</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>22330051920307</v>
-      </c>
-      <c r="B37" t="s">
-        <v>80</v>
-      </c>
-      <c r="C37" t="s">
-        <v>106</v>
-      </c>
-      <c r="D37" t="s">
-        <v>132</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>57</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>22330051920309</v>
-      </c>
-      <c r="B38" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38" t="s">
-        <v>105</v>
-      </c>
-      <c r="D38" t="s">
-        <v>134</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>57</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>22330051920310</v>
-      </c>
-      <c r="B39" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" t="s">
-        <v>107</v>
-      </c>
-      <c r="D39" t="s">
-        <v>135</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
-        <v>57</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>22330051920311</v>
-      </c>
-      <c r="B40" t="s">
-        <v>85</v>
-      </c>
-      <c r="D40" t="s">
-        <v>136</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>57</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>22330051920313</v>
-      </c>
-      <c r="B41" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" t="s">
-        <v>110</v>
-      </c>
-      <c r="D41" t="s">
-        <v>139</v>
-      </c>
-      <c r="E41" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" t="s">
-        <v>57</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>22330051920370</v>
-      </c>
-      <c r="B42" t="s">
-        <v>89</v>
-      </c>
-      <c r="C42" t="s">
-        <v>77</v>
-      </c>
-      <c r="D42" t="s">
-        <v>140</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>57</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>22330051920314</v>
-      </c>
-      <c r="B43" t="s">
-        <v>93</v>
-      </c>
-      <c r="C43" t="s">
-        <v>112</v>
-      </c>
-      <c r="D43" t="s">
-        <v>143</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G43">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>22330051920315</v>
-      </c>
-      <c r="B44" t="s">
-        <v>94</v>
-      </c>
-      <c r="C44" t="s">
-        <v>113</v>
-      </c>
-      <c r="D44" t="s">
-        <v>144</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>57</v>
-      </c>
-      <c r="G44">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ASV - Estadisticos 20222.xlsx
+++ b/grupos/2ASV - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="105">
   <si>
     <t>Materia</t>
   </si>
@@ -219,247 +218,130 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>AYALA</t>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
   </si>
   <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>CANTE</t>
-  </si>
-  <si>
     <t>CESAR</t>
   </si>
   <si>
     <t>COLOHUA</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>PUGA CABRERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OLGUIN</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CARBAJAL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>CONDE</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PUGA CABRERA</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>RAYMUNDO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>LESLIE YAMILET</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>JARED DE JESUS</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
+    <t>LUIS GUSTAVO</t>
+  </si>
+  <si>
+    <t>MIA NOEMI</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>JOSE CARMELO</t>
+  </si>
+  <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>JOSUE ISRAEL</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VALDEZ</t>
-  </si>
-  <si>
-    <t>CARBAJAL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>ISLAS</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>TOMAS RAFAEL</t>
-  </si>
-  <si>
-    <t>LUIS GUSTAVO</t>
-  </si>
-  <si>
-    <t>MIA NOEMI</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>CELINA MONSERRAT</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>ISAI</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>AARON</t>
-  </si>
-  <si>
-    <t>GAMALIEL</t>
-  </si>
-  <si>
-    <t>LESLIE YAMILET</t>
-  </si>
-  <si>
-    <t>JOSE MARCELO</t>
-  </si>
-  <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>MOISES ALBERTO</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
     <t>ALEJANDRO</t>
   </si>
   <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>ESTEPHANY</t>
-  </si>
-  <si>
-    <t>ULISES HIRAM</t>
-  </si>
-  <si>
     <t>MIRIAM AIMAR</t>
-  </si>
-  <si>
-    <t>FRANCISCO</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -512,11 +394,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -957,16 +840,16 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -993,7 +876,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>6</v>
@@ -1002,7 +885,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1034,16 +917,16 @@
         <v>7</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1070,16 +953,16 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>6</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -1111,16 +994,16 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1156,7 +1039,7 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1188,16 +1071,16 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1224,7 +1107,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>5</v>
@@ -1233,7 +1116,7 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1265,16 +1148,16 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1301,7 +1184,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>5</v>
@@ -1310,7 +1193,7 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>6</v>
@@ -1342,16 +1225,16 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1384,10 +1267,10 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1419,16 +1302,16 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1461,10 +1344,10 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1496,16 +1379,16 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1532,7 +1415,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>5</v>
@@ -1541,7 +1424,7 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -1573,16 +1456,16 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1615,10 +1498,10 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>7</v>
@@ -1650,16 +1533,16 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1695,7 +1578,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1727,16 +1610,16 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1769,10 +1652,10 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1804,16 +1687,16 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1846,10 +1729,10 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -1881,16 +1764,16 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -1917,16 +1800,16 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>5</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -1958,16 +1841,16 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -2000,10 +1883,10 @@
         <v>5</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>6</v>
@@ -2035,16 +1918,16 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2077,10 +1960,10 @@
         <v>6</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -2112,16 +1995,16 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2154,10 +2037,10 @@
         <v>7</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>10</v>
@@ -2189,16 +2072,16 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2225,13 +2108,13 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>7</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2266,16 +2149,16 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2308,10 +2191,10 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>10</v>
@@ -2343,16 +2226,16 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2379,13 +2262,13 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>5</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2420,16 +2303,16 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I23">
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2456,13 +2339,13 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>5</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2497,16 +2380,16 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I24">
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2539,10 +2422,10 @@
         <v>5</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -2574,16 +2457,16 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2610,7 +2493,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>7</v>
@@ -2619,7 +2502,7 @@
         <v>8</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -2651,16 +2534,16 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -2696,7 +2579,7 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2728,16 +2611,16 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -2764,16 +2647,16 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>5</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -2805,16 +2688,16 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -2841,13 +2724,13 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>5</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -2882,16 +2765,16 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -2927,7 +2810,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -2959,16 +2842,16 @@
         <v>6</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
         <v>-1</v>
@@ -2995,16 +2878,16 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>7</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -3036,16 +2919,16 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
         <v>-1</v>
@@ -3072,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U31">
         <v>5</v>
@@ -3081,7 +2964,7 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>9</v>
@@ -3113,16 +2996,16 @@
         <v>5</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I32">
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3149,13 +3032,13 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U32">
         <v>5</v>
       </c>
       <c r="V32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>5</v>
@@ -3190,16 +3073,16 @@
         <v>5</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I33">
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -3226,16 +3109,16 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U33">
         <v>5</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>5</v>
@@ -3267,16 +3150,16 @@
         <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I34">
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>-1</v>
@@ -3303,7 +3186,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>5</v>
@@ -3344,16 +3227,16 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L35">
         <v>-1</v>
@@ -3380,16 +3263,16 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U35">
         <v>6</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3421,16 +3304,16 @@
         <v>6</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I36">
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L36">
         <v>-1</v>
@@ -3457,7 +3340,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U36">
         <v>6</v>
@@ -3466,7 +3349,7 @@
         <v>9</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X36">
         <v>9</v>
@@ -3608,16 +3491,16 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -3667,16 +3550,16 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -3726,16 +3609,16 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -3785,16 +3668,16 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -3844,16 +3727,16 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -3903,16 +3786,16 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -3962,16 +3845,16 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -4021,16 +3904,16 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -4080,16 +3963,16 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -4139,16 +4022,16 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -4198,16 +4081,16 @@
         <v>90</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4257,16 +4140,16 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4316,16 +4199,16 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4375,16 +4258,16 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4434,16 +4317,16 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4493,16 +4376,16 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -4552,16 +4435,16 @@
         <v>90</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -4611,16 +4494,16 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -4670,16 +4553,16 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -4729,16 +4612,16 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -4788,16 +4671,16 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -4847,16 +4730,16 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -4906,16 +4789,16 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -4965,16 +4848,16 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -5024,16 +4907,16 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -5083,16 +4966,16 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -5142,16 +5025,16 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -5201,16 +5084,16 @@
         <v>95</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -5260,16 +5143,16 @@
         <v>100</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I32">
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -5319,16 +5202,16 @@
         <v>95</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -5378,16 +5261,16 @@
         <v>95</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -5437,16 +5320,16 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -5496,16 +5379,16 @@
         <v>100</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -5548,6 +5431,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -5598,11 +5483,11 @@
       <c r="E2">
         <v>15</v>
       </c>
-      <c r="F2">
-        <v>54.55</v>
-      </c>
-      <c r="G2">
-        <v>45.45</v>
+      <c r="F2" s="2">
+        <v>54.5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>45.5</v>
       </c>
       <c r="H2">
         <v>6.1</v>
@@ -5610,7 +5495,7 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5625,24 +5510,24 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>14</v>
-      </c>
-      <c r="F3">
-        <v>57.58</v>
-      </c>
-      <c r="G3">
-        <v>42.42</v>
+        <v>5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>84.8</v>
+      </c>
+      <c r="G3" s="2">
+        <v>15.2</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5662,11 +5547,11 @@
       <c r="E4">
         <v>3</v>
       </c>
-      <c r="F4">
-        <v>90.91</v>
-      </c>
-      <c r="G4">
-        <v>9.09</v>
+      <c r="F4" s="2">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="G4" s="2">
+        <v>9.1</v>
       </c>
       <c r="H4">
         <v>6.9</v>
@@ -5674,7 +5559,7 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5694,11 +5579,11 @@
       <c r="E5">
         <v>2</v>
       </c>
-      <c r="F5">
-        <v>93.94</v>
-      </c>
-      <c r="G5">
-        <v>6.06</v>
+      <c r="F5" s="2">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="G5" s="2">
+        <v>6.1</v>
       </c>
       <c r="H5">
         <v>8.4</v>
@@ -5706,48 +5591,48 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C6">
         <v>33</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>97</v>
+      </c>
+      <c r="G6" s="2">
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C7">
         <v>33</v>
@@ -5758,19 +5643,19 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+      <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5815,596 +5700,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>22330051920290</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>22330051920291</v>
-      </c>
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>22330051920293</v>
-      </c>
-      <c r="B4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>22330051920294</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>22330051920412</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>22330051920295</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>22330051920360</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>22330051920297</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>22330051920415</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>22330051920298</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" t="s">
-        <v>123</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>22330051920300</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>22330051920301</v>
-      </c>
-      <c r="B13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>22330051920302</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" t="s">
-        <v>126</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>22330051920303</v>
-      </c>
-      <c r="B15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" t="s">
-        <v>127</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>22330051920304</v>
-      </c>
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" t="s">
-        <v>128</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>22330051920305</v>
-      </c>
-      <c r="B17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" t="s">
-        <v>129</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>22330051920417</v>
-      </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>22330051920306</v>
-      </c>
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" t="s">
-        <v>131</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>22330051920307</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>106</v>
-      </c>
-      <c r="D20" t="s">
-        <v>132</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>22330051920419</v>
-      </c>
-      <c r="B21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" t="s">
-        <v>104</v>
-      </c>
-      <c r="D21" t="s">
-        <v>133</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>22330051920309</v>
-      </c>
-      <c r="B22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" t="s">
-        <v>134</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>22330051920308</v>
-      </c>
-      <c r="B23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>22330051920310</v>
-      </c>
-      <c r="B24" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" t="s">
-        <v>107</v>
-      </c>
-      <c r="D24" t="s">
-        <v>135</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>22330051920311</v>
-      </c>
-      <c r="B25" t="s">
-        <v>85</v>
-      </c>
-      <c r="D25" t="s">
-        <v>136</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>22330051920312</v>
-      </c>
-      <c r="B26" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" t="s">
-        <v>137</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>22330051920364</v>
-      </c>
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" t="s">
-        <v>138</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>22330051920313</v>
-      </c>
-      <c r="B28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" t="s">
-        <v>110</v>
-      </c>
-      <c r="D28" t="s">
-        <v>139</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>22330051920370</v>
-      </c>
-      <c r="B29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" t="s">
-        <v>77</v>
-      </c>
-      <c r="D29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>22330051920418</v>
-      </c>
-      <c r="B30" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" t="s">
-        <v>79</v>
-      </c>
-      <c r="D30" t="s">
-        <v>141</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>22330051920397</v>
-      </c>
-      <c r="B31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>89</v>
-      </c>
-      <c r="D31" t="s">
-        <v>142</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>22330051920408</v>
-      </c>
-      <c r="B32" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" t="s">
-        <v>111</v>
-      </c>
-      <c r="D32" t="s">
-        <v>133</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>22330051920314</v>
-      </c>
-      <c r="B33" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" t="s">
-        <v>143</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>22330051920315</v>
-      </c>
-      <c r="B34" t="s">
-        <v>94</v>
-      </c>
-      <c r="C34" t="s">
-        <v>113</v>
-      </c>
-      <c r="D34" t="s">
-        <v>144</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6436,22 +5732,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920294</v>
+        <v>22330051920417</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6459,22 +5755,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920294</v>
+        <v>22330051920417</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6482,16 +5778,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920412</v>
+        <v>22330051920419</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6505,16 +5801,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920412</v>
+        <v>22330051920419</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -6528,16 +5824,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920297</v>
+        <v>22330051920312</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -6551,16 +5847,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920297</v>
+        <v>22330051920312</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -6574,16 +5870,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920298</v>
+        <v>22330051920397</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -6597,16 +5893,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920298</v>
+        <v>22330051920397</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -6620,22 +5916,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920302</v>
+        <v>22330051920291</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6643,22 +5939,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920302</v>
+        <v>22330051920294</v>
       </c>
       <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" t="s">
         <v>76</v>
       </c>
-      <c r="C11" t="s">
-        <v>92</v>
-      </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6666,16 +5962,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920303</v>
+        <v>22330051920412</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -6689,22 +5985,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920303</v>
+        <v>22330051920297</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6712,22 +6008,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920417</v>
+        <v>22330051920298</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -6735,22 +6031,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920417</v>
+        <v>22330051920302</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -6758,16 +6054,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920419</v>
+        <v>22330051920303</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -6781,22 +6077,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920419</v>
+        <v>22330051920307</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -6807,13 +6103,13 @@
         <v>22330051920308</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
         <v>6</v>
@@ -6827,22 +6123,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920308</v>
+        <v>22330051920311</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -6850,16 +6143,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920312</v>
+        <v>22330051920370</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
@@ -6868,210 +6161,6 @@
         <v>57</v>
       </c>
       <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920312</v>
-      </c>
-      <c r="B21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" t="s">
-        <v>108</v>
-      </c>
-      <c r="D21" t="s">
-        <v>137</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920397</v>
-      </c>
-      <c r="B22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22" t="s">
-        <v>142</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920397</v>
-      </c>
-      <c r="B23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23" t="s">
-        <v>142</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920290</v>
-      </c>
-      <c r="B24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>58</v>
-      </c>
-      <c r="G24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920291</v>
-      </c>
-      <c r="B25" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25" t="s">
-        <v>115</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920307</v>
-      </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" t="s">
-        <v>132</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>57</v>
-      </c>
-      <c r="G26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920311</v>
-      </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" t="s">
-        <v>136</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>57</v>
-      </c>
-      <c r="G27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22330051920364</v>
-      </c>
-      <c r="B28" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" t="s">
-        <v>138</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>58</v>
-      </c>
-      <c r="G28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>22330051920370</v>
-      </c>
-      <c r="B29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" t="s">
-        <v>77</v>
-      </c>
-      <c r="D29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>57</v>
-      </c>
-      <c r="G29">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ASV - Estadisticos 20222.xlsx
+++ b/grupos/2ASV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="102">
   <si>
     <t>Materia</t>
   </si>
@@ -194,12 +194,12 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Saucedo Rivalcoba Graciela</t>
   </si>
   <si>
@@ -218,45 +218,42 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
     <t>LIBRADO</t>
   </si>
   <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
     <t>PUGA CABRERA</t>
   </si>
   <si>
@@ -266,7 +263,7 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>CORTES</t>
   </si>
   <si>
     <t>OLGUIN</t>
@@ -284,49 +281,43 @@
     <t>MORALES</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
     <t>MAYAHUA</t>
   </si>
   <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JARED DE JESUS</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
+    <t>LUIS GUSTAVO</t>
+  </si>
+  <si>
+    <t>MIA NOEMI</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>JOSE CARMELO</t>
+  </si>
+  <si>
     <t>LESLIE YAMILET</t>
   </si>
   <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>LUIS GUSTAVO</t>
-  </si>
-  <si>
-    <t>MIA NOEMI</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
     <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
@@ -855,7 +846,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -891,7 +882,7 @@
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -932,7 +923,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -968,7 +959,7 @@
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1009,7 +1000,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1086,7 +1077,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1163,7 +1154,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1240,7 +1231,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1276,7 +1267,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1317,7 +1308,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1353,7 +1344,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1394,7 +1385,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1471,7 +1462,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1507,7 +1498,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1548,7 +1539,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1584,7 +1575,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1625,7 +1616,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1661,7 +1652,7 @@
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1702,7 +1693,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1779,7 +1770,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1815,7 +1806,7 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1856,7 +1847,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1892,7 +1883,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1933,7 +1924,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1969,7 +1960,7 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2010,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2046,7 +2037,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2087,7 +2078,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2123,7 +2114,7 @@
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2164,7 +2155,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2200,7 +2191,7 @@
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2241,7 +2232,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2318,7 +2309,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2354,7 +2345,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2395,7 +2386,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2431,7 +2422,7 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2472,7 +2463,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2508,7 +2499,7 @@
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2549,7 +2540,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2626,7 +2617,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2662,7 +2653,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2703,7 +2694,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2739,7 +2730,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2780,7 +2771,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2857,7 +2848,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2893,7 +2884,7 @@
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2934,7 +2925,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3011,7 +3002,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3088,7 +3079,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3165,7 +3156,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3201,7 +3192,7 @@
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3242,7 +3233,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3278,7 +3269,7 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3319,7 +3310,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3355,7 +3346,7 @@
         <v>9</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3506,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -3565,7 +3556,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -3624,7 +3615,7 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -3683,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -3742,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -3801,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -3860,7 +3851,7 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -3919,7 +3910,7 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -3978,7 +3969,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4037,7 +4028,7 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -4096,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4155,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4214,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4273,7 +4264,7 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4332,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4391,7 +4382,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -4450,7 +4441,7 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -4509,7 +4500,7 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -4568,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -4627,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -4686,7 +4677,7 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -4745,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -4804,7 +4795,7 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -4863,7 +4854,7 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -4922,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -4981,7 +4972,7 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -5040,7 +5031,7 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -5099,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -5158,7 +5149,7 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -5217,7 +5208,7 @@
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -5276,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -5335,7 +5326,7 @@
         <v>0</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -5394,7 +5385,7 @@
         <v>0</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -5501,7 +5492,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -5510,19 +5501,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>84.8</v>
+        <v>81.8</v>
       </c>
       <c r="G3" s="2">
-        <v>15.2</v>
+        <v>18.2</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5533,7 +5524,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -5542,19 +5533,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>90.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="G4" s="2">
-        <v>9.1</v>
+        <v>15.2</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5632,7 +5623,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7">
         <v>33</v>
@@ -5732,22 +5723,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920417</v>
+        <v>22330051920302</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5755,22 +5746,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920417</v>
+        <v>22330051920302</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5778,16 +5769,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920419</v>
+        <v>22330051920303</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5801,19 +5792,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920419</v>
+        <v>22330051920303</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>58</v>
@@ -5824,16 +5815,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920312</v>
+        <v>22330051920308</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5847,19 +5838,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920312</v>
+        <v>22330051920308</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>58</v>
@@ -5870,16 +5861,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920397</v>
+        <v>22330051920312</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5893,22 +5884,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920397</v>
+        <v>22330051920312</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5916,22 +5907,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920291</v>
+        <v>22330051920397</v>
       </c>
       <c r="B10" t="s">
         <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5939,22 +5930,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920294</v>
+        <v>22330051920397</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5962,22 +5953,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920412</v>
+        <v>22330051920291</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5985,16 +5976,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920297</v>
+        <v>22330051920294</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -6008,16 +5999,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920298</v>
+        <v>22330051920412</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -6031,16 +6022,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920302</v>
+        <v>22330051920297</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
@@ -6054,16 +6045,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920303</v>
+        <v>22330051920298</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -6077,22 +6068,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920307</v>
+        <v>22330051920417</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -6100,16 +6091,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920308</v>
+        <v>22330051920307</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E18" t="s">
         <v>6</v>
@@ -6126,10 +6117,10 @@
         <v>22330051920311</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D19" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
@@ -6146,13 +6137,13 @@
         <v>22330051920370</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>

--- a/grupos/2ASV - Estadisticos 20222.xlsx
+++ b/grupos/2ASV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
   <si>
     <t>Materia</t>
   </si>
@@ -218,112 +218,88 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
     <t>LIBRADO</t>
   </si>
   <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>PUGA CABRERA</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>OLGUIN</t>
+  </si>
+  <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CARBAJAL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>MAYAHUA</t>
   </si>
   <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
     <t>ABDIEL ARMANDO</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JARED DE JESUS</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>LUIS GUSTAVO</t>
+  </si>
+  <si>
     <t>ANGEL DE JESUS</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>LUIS GUSTAVO</t>
-  </si>
-  <si>
-    <t>MIA NOEMI</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
     <t>LESLIE YAMILET</t>
   </si>
   <si>
     <t>JOSUE ISRAEL</t>
   </si>
   <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
     <t>MIRIAM AIMAR</t>
+  </si>
+  <si>
+    <t>GUILLERMO ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -834,7 +810,7 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>8</v>
@@ -870,7 +846,7 @@
         <v>9</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -911,7 +887,7 @@
         <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>7</v>
@@ -947,7 +923,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V5">
         <v>7</v>
@@ -988,7 +964,7 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>9</v>
@@ -1024,7 +1000,7 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -1065,7 +1041,7 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>9</v>
@@ -1142,7 +1118,7 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>9</v>
@@ -1178,7 +1154,7 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1219,7 +1195,7 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>8</v>
@@ -1255,7 +1231,7 @@
         <v>9</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>8</v>
@@ -1296,7 +1272,7 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>8</v>
@@ -1332,7 +1308,7 @@
         <v>9</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>8</v>
@@ -1373,7 +1349,7 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>9</v>
@@ -1409,7 +1385,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1450,7 +1426,7 @@
         <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>7</v>
@@ -1486,7 +1462,7 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -1527,7 +1503,7 @@
         <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>9</v>
@@ -1604,7 +1580,7 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
         <v>8</v>
@@ -1681,7 +1657,7 @@
         <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>7</v>
@@ -1717,7 +1693,7 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -1758,7 +1734,7 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>7</v>
@@ -1835,7 +1811,7 @@
         <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
         <v>8</v>
@@ -1871,7 +1847,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -1912,7 +1888,7 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>7</v>
@@ -1948,7 +1924,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -1989,7 +1965,7 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
         <v>7</v>
@@ -2025,7 +2001,7 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>7</v>
@@ -2066,7 +2042,7 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>9</v>
@@ -2143,7 +2119,7 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>7</v>
@@ -2220,7 +2196,7 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>8</v>
@@ -2297,7 +2273,7 @@
         <v>4</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>8</v>
@@ -2374,7 +2350,7 @@
         <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>8</v>
@@ -2451,7 +2427,7 @@
         <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>8</v>
@@ -2528,7 +2504,7 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
         <v>9</v>
@@ -2564,7 +2540,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -2605,7 +2581,7 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>7</v>
@@ -2641,7 +2617,7 @@
         <v>9</v>
       </c>
       <c r="U27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>7</v>
@@ -2682,7 +2658,7 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
         <v>7</v>
@@ -2759,7 +2735,7 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
         <v>9</v>
@@ -2795,7 +2771,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2836,7 +2812,7 @@
         <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
         <v>8</v>
@@ -2872,7 +2848,7 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>8</v>
@@ -2913,7 +2889,7 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>9</v>
@@ -2990,7 +2966,7 @@
         <v>4</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
         <v>7</v>
@@ -3067,7 +3043,7 @@
         <v>4</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>7</v>
@@ -3144,7 +3120,7 @@
         <v>6</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>9</v>
@@ -3221,7 +3197,7 @@
         <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
         <v>8</v>
@@ -3257,7 +3233,7 @@
         <v>8</v>
       </c>
       <c r="U35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -3298,7 +3274,7 @@
         <v>7</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
         <v>9</v>
@@ -3485,7 +3461,7 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -3544,7 +3520,7 @@
         <v>94</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -3603,7 +3579,7 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3662,7 +3638,7 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -3721,7 +3697,7 @@
         <v>98</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -3780,7 +3756,7 @@
         <v>98</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -3839,7 +3815,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -3898,7 +3874,7 @@
         <v>94</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -3957,7 +3933,7 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -4016,7 +3992,7 @@
         <v>98</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -4075,7 +4051,7 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -4134,7 +4110,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -4193,7 +4169,7 @@
         <v>98</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -4252,7 +4228,7 @@
         <v>96</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17">
         <v>100</v>
@@ -4311,7 +4287,7 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -4370,7 +4346,7 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J19">
         <v>100</v>
@@ -4429,7 +4405,7 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J20">
         <v>100</v>
@@ -4488,7 +4464,7 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -4547,7 +4523,7 @@
         <v>98</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J22">
         <v>100</v>
@@ -4606,7 +4582,7 @@
         <v>90</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -4665,7 +4641,7 @@
         <v>96</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J24">
         <v>100</v>
@@ -4724,7 +4700,7 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
         <v>100</v>
@@ -4783,7 +4759,7 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -4842,7 +4818,7 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J27">
         <v>100</v>
@@ -4901,7 +4877,7 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J28">
         <v>100</v>
@@ -4960,7 +4936,7 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J29">
         <v>100</v>
@@ -5019,7 +4995,7 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -5078,7 +5054,7 @@
         <v>96</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J31">
         <v>100</v>
@@ -5137,7 +5113,7 @@
         <v>90</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J32">
         <v>100</v>
@@ -5196,7 +5172,7 @@
         <v>90</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J33">
         <v>100</v>
@@ -5255,7 +5231,7 @@
         <v>96</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J34">
         <v>100</v>
@@ -5314,7 +5290,7 @@
         <v>96</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J35">
         <v>100</v>
@@ -5373,7 +5349,7 @@
         <v>100</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J36">
         <v>100</v>
@@ -5469,19 +5445,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>54.5</v>
+        <v>63.6</v>
       </c>
       <c r="G2" s="2">
-        <v>45.5</v>
+        <v>36.4</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5691,7 +5667,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5723,16 +5699,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920302</v>
+        <v>22330051920291</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5746,22 +5722,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920302</v>
+        <v>22330051920291</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5769,16 +5745,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920303</v>
+        <v>22330051920302</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5792,16 +5768,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920303</v>
+        <v>22330051920302</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5821,10 +5797,10 @@
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5844,10 +5820,10 @@
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5867,10 +5843,10 @@
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5890,10 +5866,10 @@
         <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -5913,10 +5889,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5936,10 +5912,10 @@
         <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -5953,22 +5929,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920291</v>
+        <v>22330051920294</v>
       </c>
       <c r="B12" t="s">
         <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5976,22 +5952,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920294</v>
+        <v>22330051920303</v>
       </c>
       <c r="B13" t="s">
         <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5999,22 +5975,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920412</v>
+        <v>22330051920417</v>
       </c>
       <c r="B14" t="s">
         <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -6022,16 +5998,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920297</v>
+        <v>22330051920307</v>
       </c>
       <c r="B15" t="s">
         <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
@@ -6045,16 +6021,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920298</v>
+        <v>22330051920370</v>
       </c>
       <c r="B16" t="s">
         <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -6068,90 +6044,24 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920417</v>
+        <v>22330051920314</v>
       </c>
       <c r="B17" t="s">
         <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920307</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" t="s">
-        <v>99</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920311</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920370</v>
-      </c>
-      <c r="B20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ASV - Estadisticos 20222.xlsx
+++ b/grupos/2ASV - Estadisticos 20222.xlsx
@@ -819,7 +819,7 @@
         <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>8</v>
@@ -896,7 +896,7 @@
         <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -973,7 +973,7 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -1050,7 +1050,7 @@
         <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>7</v>
@@ -1127,7 +1127,7 @@
         <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>7</v>
@@ -1163,7 +1163,7 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1204,7 +1204,7 @@
         <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -1281,7 +1281,7 @@
         <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -1358,7 +1358,7 @@
         <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>7</v>
@@ -1435,7 +1435,7 @@
         <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>7</v>
@@ -1471,7 +1471,7 @@
         <v>6</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1512,7 +1512,7 @@
         <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -1589,7 +1589,7 @@
         <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -1666,7 +1666,7 @@
         <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>7</v>
@@ -1743,7 +1743,7 @@
         <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -1779,7 +1779,7 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -1820,7 +1820,7 @@
         <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>5</v>
@@ -1856,7 +1856,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -1897,7 +1897,7 @@
         <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>8</v>
@@ -1933,7 +1933,7 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -1974,7 +1974,7 @@
         <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>7</v>
@@ -2051,7 +2051,7 @@
         <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>7</v>
@@ -2087,7 +2087,7 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2128,7 +2128,7 @@
         <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>8</v>
@@ -2205,7 +2205,7 @@
         <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
         <v>7</v>
@@ -2241,7 +2241,7 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2282,7 +2282,7 @@
         <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -2318,7 +2318,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2359,7 +2359,7 @@
         <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -2395,7 +2395,7 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2436,7 +2436,7 @@
         <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
         <v>8</v>
@@ -2472,7 +2472,7 @@
         <v>8</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -2513,7 +2513,7 @@
         <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -2590,7 +2590,7 @@
         <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
         <v>8</v>
@@ -2626,7 +2626,7 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -2667,7 +2667,7 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
         <v>7</v>
@@ -2744,7 +2744,7 @@
         <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -2821,7 +2821,7 @@
         <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>9</v>
@@ -2898,7 +2898,7 @@
         <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
         <v>6</v>
@@ -2975,7 +2975,7 @@
         <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>5</v>
@@ -3011,7 +3011,7 @@
         <v>5</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y32">
         <v>5</v>
@@ -3052,7 +3052,7 @@
         <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>5</v>
@@ -3129,7 +3129,7 @@
         <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>8</v>
@@ -3165,7 +3165,7 @@
         <v>5</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -3206,7 +3206,7 @@
         <v>7</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
         <v>5</v>
@@ -3242,7 +3242,7 @@
         <v>7</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>6</v>
@@ -3283,7 +3283,7 @@
         <v>7</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M36">
         <v>7</v>
@@ -3319,7 +3319,7 @@
         <v>7</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>7</v>
@@ -3470,7 +3470,7 @@
         <v>94.3</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
         <v>95</v>
@@ -3529,7 +3529,7 @@
         <v>94.3</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M5">
         <v>95</v>
@@ -3588,7 +3588,7 @@
         <v>94.3</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -3647,7 +3647,7 @@
         <v>94.3</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -3706,7 +3706,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M8">
         <v>95</v>
@@ -3765,7 +3765,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -3824,7 +3824,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -3883,7 +3883,7 @@
         <v>94.3</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -3942,7 +3942,7 @@
         <v>94.3</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -4001,7 +4001,7 @@
         <v>94.3</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -4060,7 +4060,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -4119,7 +4119,7 @@
         <v>94.3</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -4178,7 +4178,7 @@
         <v>94.3</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M16">
         <v>75</v>
@@ -4237,7 +4237,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17">
         <v>95</v>
@@ -4296,7 +4296,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -4355,7 +4355,7 @@
         <v>94.3</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -4414,7 +4414,7 @@
         <v>94.3</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M20">
         <v>95</v>
@@ -4473,7 +4473,7 @@
         <v>94.3</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -4532,7 +4532,7 @@
         <v>94.3</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M22">
         <v>100</v>
@@ -4591,7 +4591,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M23">
         <v>75</v>
@@ -4650,7 +4650,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -4709,7 +4709,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M25">
         <v>100</v>
@@ -4768,7 +4768,7 @@
         <v>94.3</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -4827,7 +4827,7 @@
         <v>94.3</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27">
         <v>100</v>
@@ -4886,7 +4886,7 @@
         <v>94.3</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M28">
         <v>100</v>
@@ -4945,7 +4945,7 @@
         <v>94.3</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -5004,7 +5004,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -5063,7 +5063,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M31">
         <v>90</v>
@@ -5122,7 +5122,7 @@
         <v>94.3</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M32">
         <v>80</v>
@@ -5181,7 +5181,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M33">
         <v>75</v>
@@ -5240,7 +5240,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M34">
         <v>90</v>
@@ -5299,7 +5299,7 @@
         <v>94.3</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M35">
         <v>90</v>
@@ -5358,7 +5358,7 @@
         <v>94.3</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M36">
         <v>100</v>
@@ -5541,19 +5541,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>93.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>6.1</v>
+        <v>9.1</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>

--- a/grupos/2ASV - Estadisticos 20222.xlsx
+++ b/grupos/2ASV - Estadisticos 20222.xlsx
@@ -3443,13 +3443,13 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>100</v>
       </c>
       <c r="E4">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -3461,37 +3461,37 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J4">
         <v>100</v>
       </c>
       <c r="K4">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3502,13 +3502,13 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>100</v>
       </c>
       <c r="E5">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>95</v>
@@ -3517,40 +3517,40 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I5">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L5">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="M5">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3561,13 +3561,13 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>100</v>
       </c>
       <c r="E6">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -3579,13 +3579,13 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>100</v>
       </c>
       <c r="K6">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -3594,22 +3594,22 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3620,13 +3620,13 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="D7">
         <v>100</v>
       </c>
       <c r="E7">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>90</v>
@@ -3638,37 +3638,37 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J7">
         <v>100</v>
       </c>
       <c r="K7">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L7">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="M7">
         <v>100</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3679,13 +3679,13 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>95</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D8">
         <v>100</v>
       </c>
       <c r="E8">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>90</v>
@@ -3694,40 +3694,40 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I8">
-        <v>90</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="J8">
         <v>100</v>
       </c>
       <c r="K8">
-        <v>91.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="L8">
         <v>90</v>
       </c>
       <c r="M8">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3738,13 +3738,13 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>100</v>
       </c>
       <c r="E9">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -3753,16 +3753,16 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J9">
         <v>100</v>
       </c>
       <c r="K9">
-        <v>91.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -3771,22 +3771,22 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3797,13 +3797,13 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>100</v>
       </c>
       <c r="E10">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -3815,13 +3815,13 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J10">
         <v>100</v>
       </c>
       <c r="K10">
-        <v>91.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -3830,22 +3830,22 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3856,13 +3856,13 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>100</v>
       </c>
       <c r="E11">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>100</v>
@@ -3871,40 +3871,40 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I11">
-        <v>105</v>
+        <v>97.7</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M11">
         <v>100</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3915,13 +3915,13 @@
         <v>100</v>
       </c>
       <c r="C12">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>100</v>
       </c>
       <c r="E12">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -3933,37 +3933,37 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>105</v>
+        <v>97.7</v>
       </c>
       <c r="J12">
         <v>100</v>
       </c>
       <c r="K12">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L12">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M12">
         <v>100</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3974,13 +3974,13 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>100</v>
       </c>
       <c r="E13">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F13">
         <v>100</v>
@@ -3989,40 +3989,40 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I13">
-        <v>105</v>
+        <v>97.7</v>
       </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M13">
         <v>100</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4033,13 +4033,13 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>100</v>
       </c>
       <c r="E14">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>95</v>
@@ -4051,37 +4051,37 @@
         <v>100</v>
       </c>
       <c r="I14">
+        <v>93.2</v>
+      </c>
+      <c r="J14">
+        <v>100</v>
+      </c>
+      <c r="K14">
+        <v>98.5</v>
+      </c>
+      <c r="L14">
+        <v>97.5</v>
+      </c>
+      <c r="M14">
         <v>95</v>
       </c>
-      <c r="J14">
-        <v>100</v>
-      </c>
-      <c r="K14">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="L14">
-        <v>100</v>
-      </c>
-      <c r="M14">
-        <v>100</v>
-      </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4092,13 +4092,13 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>100</v>
       </c>
       <c r="E15">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>100</v>
@@ -4110,13 +4110,13 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J15">
         <v>100</v>
       </c>
       <c r="K15">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -4125,22 +4125,22 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4151,13 +4151,13 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>80</v>
+        <v>72.7</v>
       </c>
       <c r="D16">
         <v>100</v>
       </c>
       <c r="E16">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>95</v>
@@ -4166,40 +4166,40 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I16">
-        <v>70</v>
+        <v>68.2</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L16">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M16">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>68.2</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4210,13 +4210,13 @@
         <v>100</v>
       </c>
       <c r="C17">
-        <v>95</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D17">
         <v>100</v>
       </c>
       <c r="E17">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>90</v>
@@ -4225,40 +4225,40 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I17">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J17">
         <v>100</v>
       </c>
       <c r="K17">
-        <v>91.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="L17">
         <v>90</v>
       </c>
       <c r="M17">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4269,13 +4269,13 @@
         <v>100</v>
       </c>
       <c r="C18">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="D18">
         <v>100</v>
       </c>
       <c r="E18">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>90</v>
@@ -4287,37 +4287,37 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>110</v>
+        <v>97.7</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>91.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M18">
         <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4328,13 +4328,13 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>100</v>
       </c>
       <c r="E19">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>95</v>
@@ -4346,37 +4346,37 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J19">
         <v>100</v>
       </c>
       <c r="K19">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M19">
         <v>100</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4387,13 +4387,13 @@
         <v>100</v>
       </c>
       <c r="C20">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>100</v>
       </c>
       <c r="E20">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>95</v>
@@ -4405,37 +4405,37 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>105</v>
+        <v>97.7</v>
       </c>
       <c r="J20">
         <v>100</v>
       </c>
       <c r="K20">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>95</v>
       </c>
       <c r="M20">
+        <v>92.5</v>
+      </c>
+      <c r="N20">
+        <v>100</v>
+      </c>
+      <c r="O20">
+        <v>97.7</v>
+      </c>
+      <c r="P20">
+        <v>100</v>
+      </c>
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
         <v>95</v>
       </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
       <c r="S20">
-        <v>0</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4446,13 +4446,13 @@
         <v>100</v>
       </c>
       <c r="C21">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>100</v>
       </c>
       <c r="E21">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -4464,13 +4464,13 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -4479,22 +4479,22 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4505,13 +4505,13 @@
         <v>100</v>
       </c>
       <c r="C22">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D22">
         <v>100</v>
       </c>
       <c r="E22">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>95</v>
@@ -4520,40 +4520,40 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I22">
-        <v>85</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L22">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="M22">
         <v>100</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4564,13 +4564,13 @@
         <v>100</v>
       </c>
       <c r="C23">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D23">
         <v>100</v>
       </c>
       <c r="E23">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>95</v>
@@ -4579,40 +4579,40 @@
         <v>100</v>
       </c>
       <c r="H23">
+        <v>95</v>
+      </c>
+      <c r="I23">
+        <v>77.3</v>
+      </c>
+      <c r="J23">
+        <v>100</v>
+      </c>
+      <c r="K23">
+        <v>98.5</v>
+      </c>
+      <c r="L23">
         <v>90</v>
       </c>
-      <c r="I23">
-        <v>70</v>
-      </c>
-      <c r="J23">
-        <v>100</v>
-      </c>
-      <c r="K23">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="L23">
-        <v>85</v>
-      </c>
       <c r="M23">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>77.3</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4623,13 +4623,13 @@
         <v>100</v>
       </c>
       <c r="C24">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>100</v>
       </c>
       <c r="E24">
-        <v>91.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -4638,40 +4638,40 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I24">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J24">
         <v>100</v>
       </c>
       <c r="K24">
-        <v>91.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="L24">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M24">
         <v>100</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4682,13 +4682,13 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>100</v>
       </c>
       <c r="E25">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>100</v>
@@ -4700,37 +4700,37 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J25">
         <v>100</v>
       </c>
       <c r="K25">
-        <v>91.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="L25">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M25">
         <v>100</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4741,13 +4741,13 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>100</v>
       </c>
       <c r="E26">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -4759,13 +4759,13 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -4774,22 +4774,22 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4800,13 +4800,13 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>100</v>
       </c>
       <c r="E27">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>100</v>
@@ -4818,13 +4818,13 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J27">
         <v>100</v>
       </c>
       <c r="K27">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -4833,22 +4833,22 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4859,13 +4859,13 @@
         <v>100</v>
       </c>
       <c r="C28">
-        <v>85</v>
+        <v>77.3</v>
       </c>
       <c r="D28">
         <v>100</v>
       </c>
       <c r="E28">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F28">
         <v>95</v>
@@ -4877,13 +4877,13 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>110</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>95</v>
@@ -4892,22 +4892,22 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4918,13 +4918,13 @@
         <v>100</v>
       </c>
       <c r="C29">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>100</v>
       </c>
       <c r="E29">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>100</v>
@@ -4936,13 +4936,13 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J29">
         <v>100</v>
       </c>
       <c r="K29">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -4951,22 +4951,22 @@
         <v>100</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4977,13 +4977,13 @@
         <v>100</v>
       </c>
       <c r="C30">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>100</v>
       </c>
       <c r="E30">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>100</v>
@@ -4995,13 +4995,13 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J30">
         <v>100</v>
       </c>
       <c r="K30">
-        <v>91.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -5010,22 +5010,22 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5036,13 +5036,13 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>80</v>
+        <v>72.7</v>
       </c>
       <c r="D31">
         <v>100</v>
       </c>
       <c r="E31">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F31">
         <v>95</v>
@@ -5051,40 +5051,40 @@
         <v>95</v>
       </c>
       <c r="H31">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I31">
-        <v>90</v>
+        <v>77.3</v>
       </c>
       <c r="J31">
         <v>100</v>
       </c>
       <c r="K31">
-        <v>91.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="L31">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="M31">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>77.3</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5095,13 +5095,13 @@
         <v>100</v>
       </c>
       <c r="C32">
-        <v>80</v>
+        <v>72.7</v>
       </c>
       <c r="D32">
         <v>100</v>
       </c>
       <c r="E32">
-        <v>85.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F32">
         <v>90</v>
@@ -5110,40 +5110,40 @@
         <v>100</v>
       </c>
       <c r="H32">
+        <v>95</v>
+      </c>
+      <c r="I32">
+        <v>77.3</v>
+      </c>
+      <c r="J32">
+        <v>100</v>
+      </c>
+      <c r="K32">
+        <v>95.5</v>
+      </c>
+      <c r="L32">
+        <v>87.5</v>
+      </c>
+      <c r="M32">
         <v>90</v>
       </c>
-      <c r="I32">
+      <c r="N32">
+        <v>95</v>
+      </c>
+      <c r="O32">
+        <v>77.3</v>
+      </c>
+      <c r="P32">
+        <v>100</v>
+      </c>
+      <c r="Q32">
+        <v>95.5</v>
+      </c>
+      <c r="R32">
+        <v>87.5</v>
+      </c>
+      <c r="S32">
         <v>90</v>
-      </c>
-      <c r="J32">
-        <v>100</v>
-      </c>
-      <c r="K32">
-        <v>94.3</v>
-      </c>
-      <c r="L32">
-        <v>85</v>
-      </c>
-      <c r="M32">
-        <v>80</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5154,13 +5154,13 @@
         <v>100</v>
       </c>
       <c r="C33">
-        <v>75</v>
+        <v>68.2</v>
       </c>
       <c r="D33">
         <v>100</v>
       </c>
       <c r="E33">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F33">
         <v>90</v>
@@ -5169,40 +5169,40 @@
         <v>95</v>
       </c>
       <c r="H33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I33">
-        <v>80</v>
+        <v>70.5</v>
       </c>
       <c r="J33">
         <v>100</v>
       </c>
       <c r="K33">
-        <v>91.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="L33">
+        <v>87.5</v>
+      </c>
+      <c r="M33">
         <v>85</v>
       </c>
-      <c r="M33">
-        <v>75</v>
-      </c>
       <c r="N33">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>70.5</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5213,13 +5213,13 @@
         <v>100</v>
       </c>
       <c r="C34">
-        <v>80</v>
+        <v>72.7</v>
       </c>
       <c r="D34">
         <v>100</v>
       </c>
       <c r="E34">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F34">
         <v>100</v>
@@ -5228,40 +5228,40 @@
         <v>95</v>
       </c>
       <c r="H34">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I34">
-        <v>90</v>
+        <v>77.3</v>
       </c>
       <c r="J34">
         <v>100</v>
       </c>
       <c r="K34">
-        <v>91.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="L34">
         <v>100</v>
       </c>
       <c r="M34">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>77.3</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5272,13 +5272,13 @@
         <v>100</v>
       </c>
       <c r="C35">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="D35">
         <v>100</v>
       </c>
       <c r="E35">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F35">
         <v>95</v>
@@ -5287,40 +5287,40 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I35">
-        <v>80</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="J35">
         <v>100</v>
       </c>
       <c r="K35">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L35">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M35">
+        <v>95</v>
+      </c>
+      <c r="N35">
+        <v>98</v>
+      </c>
+      <c r="O35">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="P35">
+        <v>100</v>
+      </c>
+      <c r="Q35">
+        <v>100</v>
+      </c>
+      <c r="R35">
         <v>90</v>
       </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>0</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
       <c r="S35">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5331,13 +5331,13 @@
         <v>100</v>
       </c>
       <c r="C36">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D36">
         <v>100</v>
       </c>
       <c r="E36">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F36">
         <v>95</v>
@@ -5349,13 +5349,13 @@
         <v>100</v>
       </c>
       <c r="I36">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J36">
         <v>100</v>
       </c>
       <c r="K36">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L36">
         <v>95</v>
@@ -5364,22 +5364,22 @@
         <v>100</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ASV - Estadisticos 20222.xlsx
+++ b/grupos/2ASV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="94">
   <si>
     <t>Materia</t>
   </si>
@@ -218,21 +218,21 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
     <t>CESAR</t>
   </si>
   <si>
@@ -251,15 +251,15 @@
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>OLGUIN</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
     <t>CORTES</t>
   </si>
   <si>
@@ -269,19 +269,19 @@
     <t>PAZ</t>
   </si>
   <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JARED DE JESUS</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
     <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
   </si>
   <si>
     <t>LUIS GUSTAVO</t>
@@ -837,7 +837,7 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -914,7 +914,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -932,7 +932,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -991,7 +991,7 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1068,7 +1068,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1086,7 +1086,7 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1145,7 +1145,7 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1222,7 +1222,7 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1299,7 +1299,7 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1376,7 +1376,7 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1394,7 +1394,7 @@
         <v>6</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1453,7 +1453,7 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1471,7 +1471,7 @@
         <v>6</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1530,7 +1530,7 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1607,7 +1607,7 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1684,7 +1684,7 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1761,7 +1761,7 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1779,7 +1779,7 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -1838,7 +1838,7 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -1915,7 +1915,7 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -1992,7 +1992,7 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2010,7 +2010,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2069,7 +2069,7 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2146,7 +2146,7 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2223,7 +2223,7 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2300,7 +2300,7 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2318,7 +2318,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2377,7 +2377,7 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2395,7 +2395,7 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2454,7 +2454,7 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2472,7 +2472,7 @@
         <v>8</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2608,7 +2608,7 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2685,7 +2685,7 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2703,7 +2703,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2762,7 +2762,7 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -2839,7 +2839,7 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -2916,7 +2916,7 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -2993,7 +2993,7 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3011,7 +3011,7 @@
         <v>5</v>
       </c>
       <c r="X32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>5</v>
@@ -3070,7 +3070,7 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3147,7 +3147,7 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3165,7 +3165,7 @@
         <v>5</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -3224,7 +3224,7 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3242,7 +3242,7 @@
         <v>7</v>
       </c>
       <c r="X35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>6</v>
@@ -3301,7 +3301,7 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3547,7 +3547,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="S5">
         <v>97.5</v>
@@ -3665,7 +3665,7 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -3724,7 +3724,7 @@
         <v>98.5</v>
       </c>
       <c r="R8">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S8">
         <v>97.5</v>
@@ -3901,7 +3901,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -3960,7 +3960,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -4019,7 +4019,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -4078,7 +4078,7 @@
         <v>98.5</v>
       </c>
       <c r="R14">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S14">
         <v>95</v>
@@ -4196,7 +4196,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S16">
         <v>87.5</v>
@@ -4255,7 +4255,7 @@
         <v>98.5</v>
       </c>
       <c r="R17">
-        <v>90</v>
+        <v>92.2</v>
       </c>
       <c r="S17">
         <v>97.5</v>
@@ -4314,7 +4314,7 @@
         <v>98.5</v>
       </c>
       <c r="R18">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -4373,7 +4373,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -4432,7 +4432,7 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S20">
         <v>92.5</v>
@@ -4550,7 +4550,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -4609,7 +4609,7 @@
         <v>98.5</v>
       </c>
       <c r="R23">
-        <v>90</v>
+        <v>56.3</v>
       </c>
       <c r="S23">
         <v>87.5</v>
@@ -4668,7 +4668,7 @@
         <v>97</v>
       </c>
       <c r="R24">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -4727,7 +4727,7 @@
         <v>98.5</v>
       </c>
       <c r="R25">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -4904,7 +4904,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -5081,7 +5081,7 @@
         <v>98.5</v>
       </c>
       <c r="R31">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="S31">
         <v>92.5</v>
@@ -5140,7 +5140,7 @@
         <v>95.5</v>
       </c>
       <c r="R32">
-        <v>87.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S32">
         <v>90</v>
@@ -5199,7 +5199,7 @@
         <v>98.5</v>
       </c>
       <c r="R33">
-        <v>87.5</v>
+        <v>54.7</v>
       </c>
       <c r="S33">
         <v>85</v>
@@ -5258,7 +5258,7 @@
         <v>98.5</v>
       </c>
       <c r="R34">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S34">
         <v>92.5</v>
@@ -5317,7 +5317,7 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>90</v>
+        <v>92.2</v>
       </c>
       <c r="S35">
         <v>95</v>
@@ -5376,7 +5376,7 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -5541,19 +5541,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>90.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5667,7 +5667,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5699,7 +5699,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920291</v>
+        <v>22330051920302</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920291</v>
+        <v>22330051920302</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -5734,10 +5734,10 @@
         <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5745,13 +5745,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920302</v>
+        <v>22330051920308</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
         <v>84</v>
@@ -5768,13 +5768,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920302</v>
+        <v>22330051920308</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
         <v>84</v>
@@ -5791,13 +5791,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920308</v>
+        <v>22330051920312</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
         <v>85</v>
@@ -5814,22 +5814,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920308</v>
+        <v>22330051920312</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
         <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5837,13 +5837,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920312</v>
+        <v>22330051920397</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
         <v>86</v>
@@ -5860,13 +5860,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920312</v>
+        <v>22330051920397</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
         <v>86</v>
@@ -5883,13 +5883,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920397</v>
+        <v>22330051920291</v>
       </c>
       <c r="B10" t="s">
         <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
         <v>87</v>
@@ -5906,22 +5906,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920397</v>
+        <v>22330051920294</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920294</v>
+        <v>22330051920303</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5952,22 +5952,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920303</v>
+        <v>22330051920417</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5975,22 +5975,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920417</v>
+        <v>22330051920307</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5998,16 +5998,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920307</v>
+        <v>22330051920370</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
@@ -6021,16 +6021,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920370</v>
+        <v>22330051920314</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -6039,29 +6039,6 @@
         <v>57</v>
       </c>
       <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920314</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ASV - Estadisticos 20222.xlsx
+++ b/grupos/2ASV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="94">
   <si>
     <t>Materia</t>
   </si>
@@ -197,15 +197,15 @@
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
+    <t>Saucedo Rivalcoba Graciela</t>
+  </si>
+  <si>
+    <t>Sánchez Sánchez Miguel</t>
+  </si>
+  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Saucedo Rivalcoba Graciela</t>
-  </si>
-  <si>
-    <t>Sánchez Sánchez Miguel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -224,48 +224,48 @@
     <t>PANTOJA</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>QUESADA</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>SANTOS</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
   </si>
   <si>
     <t>OLGUIN</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
@@ -275,28 +275,28 @@
     <t>SANTIAGO</t>
   </si>
   <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
+    <t>LUIS GUSTAVO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>JOSUE ISRAEL</t>
+  </si>
+  <si>
     <t>JARED DE JESUS</t>
   </si>
   <si>
+    <t>MIRIAM AIMAR</t>
+  </si>
+  <si>
     <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>LUIS GUSTAVO</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>LESLIE YAMILET</t>
-  </si>
-  <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>MIRIAM AIMAR</t>
   </si>
   <si>
     <t>GUILLERMO ALEXANDER</t>
@@ -825,16 +825,16 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>10</v>
@@ -852,7 +852,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -902,16 +902,16 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
         <v>8</v>
@@ -926,10 +926,10 @@
         <v>5</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -979,16 +979,16 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
         <v>9</v>
@@ -1003,10 +1003,10 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1056,16 +1056,16 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
         <v>8</v>
@@ -1133,16 +1133,16 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
         <v>8</v>
@@ -1210,16 +1210,16 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
         <v>9</v>
@@ -1228,7 +1228,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -1287,16 +1287,16 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>10</v>
@@ -1364,16 +1364,16 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
         <v>8</v>
@@ -1441,16 +1441,16 @@
         <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
         <v>7</v>
@@ -1465,7 +1465,7 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1518,16 +1518,16 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>10</v>
@@ -1536,7 +1536,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -1545,7 +1545,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1595,16 +1595,16 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>10</v>
@@ -1619,7 +1619,7 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1672,16 +1672,16 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>9</v>
@@ -1690,7 +1690,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -1749,16 +1749,16 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>8</v>
@@ -1767,13 +1767,13 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>5</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -1826,16 +1826,16 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>9</v>
@@ -1850,7 +1850,7 @@
         <v>6</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>6</v>
@@ -1903,16 +1903,16 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
         <v>9</v>
@@ -1921,7 +1921,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -1980,16 +1980,16 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
         <v>8</v>
@@ -2057,16 +2057,16 @@
         <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
         <v>8</v>
@@ -2075,16 +2075,16 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>7</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2134,16 +2134,16 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
         <v>9</v>
@@ -2211,16 +2211,16 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>10</v>
@@ -2235,7 +2235,7 @@
         <v>5</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2288,16 +2288,16 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
         <v>5</v>
@@ -2306,13 +2306,13 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>5</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2365,16 +2365,16 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
         <v>10</v>
@@ -2383,7 +2383,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>5</v>
@@ -2442,16 +2442,16 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
         <v>8</v>
@@ -2469,7 +2469,7 @@
         <v>8</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -2519,16 +2519,16 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>10</v>
@@ -2546,7 +2546,7 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2596,16 +2596,16 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>10</v>
@@ -2673,16 +2673,16 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
         <v>6</v>
@@ -2700,7 +2700,7 @@
         <v>7</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -2750,16 +2750,16 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>10</v>
@@ -2827,16 +2827,16 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
         <v>10</v>
@@ -2851,10 +2851,10 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -2904,16 +2904,16 @@
         <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
         <v>10</v>
@@ -2931,7 +2931,7 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>9</v>
@@ -2981,16 +2981,16 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
         <v>7</v>
@@ -2999,16 +2999,16 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>5</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>6</v>
@@ -3058,16 +3058,16 @@
         <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O33">
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
         <v>5</v>
@@ -3076,16 +3076,16 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U33">
         <v>5</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>5</v>
@@ -3135,16 +3135,16 @@
         <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R34">
         <v>10</v>
@@ -3159,10 +3159,10 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>8</v>
@@ -3212,16 +3212,16 @@
         <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O35">
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R35">
         <v>7</v>
@@ -3230,16 +3230,16 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U35">
         <v>5</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>7</v>
@@ -3289,16 +3289,16 @@
         <v>7</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O36">
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R36">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U36">
         <v>6</v>
@@ -3485,7 +3485,7 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -3535,7 +3535,7 @@
         <v>97.5</v>
       </c>
       <c r="N5">
-        <v>97</v>
+        <v>97.5</v>
       </c>
       <c r="O5">
         <v>93.2</v>
@@ -3544,7 +3544,7 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R5">
         <v>92.2</v>
@@ -3653,7 +3653,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="O7">
         <v>88.59999999999999</v>
@@ -3712,7 +3712,7 @@
         <v>97.5</v>
       </c>
       <c r="N8">
-        <v>99</v>
+        <v>98.8</v>
       </c>
       <c r="O8">
         <v>84.09999999999999</v>
@@ -3721,7 +3721,7 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="R8">
         <v>90.59999999999999</v>
@@ -3771,16 +3771,16 @@
         <v>100</v>
       </c>
       <c r="N9">
+        <v>98.8</v>
+      </c>
+      <c r="O9">
+        <v>100</v>
+      </c>
+      <c r="P9">
+        <v>100</v>
+      </c>
+      <c r="Q9">
         <v>99</v>
-      </c>
-      <c r="O9">
-        <v>100</v>
-      </c>
-      <c r="P9">
-        <v>100</v>
-      </c>
-      <c r="Q9">
-        <v>98.5</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -3839,7 +3839,7 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -3889,7 +3889,7 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>97</v>
+        <v>96.3</v>
       </c>
       <c r="O11">
         <v>97.7</v>
@@ -4007,7 +4007,7 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>99</v>
+        <v>98.8</v>
       </c>
       <c r="O13">
         <v>97.7</v>
@@ -4066,7 +4066,7 @@
         <v>95</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O14">
         <v>93.2</v>
@@ -4075,7 +4075,7 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>98.5</v>
+        <v>98</v>
       </c>
       <c r="R14">
         <v>98.40000000000001</v>
@@ -4134,7 +4134,7 @@
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -4184,7 +4184,7 @@
         <v>87.5</v>
       </c>
       <c r="N16">
-        <v>99</v>
+        <v>96.3</v>
       </c>
       <c r="O16">
         <v>68.2</v>
@@ -4193,7 +4193,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R16">
         <v>90.59999999999999</v>
@@ -4243,7 +4243,7 @@
         <v>97.5</v>
       </c>
       <c r="N17">
-        <v>98</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="O17">
         <v>88.59999999999999</v>
@@ -4252,7 +4252,7 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="R17">
         <v>92.2</v>
@@ -4311,7 +4311,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="R18">
         <v>95.3</v>
@@ -4420,7 +4420,7 @@
         <v>92.5</v>
       </c>
       <c r="N20">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O20">
         <v>97.7</v>
@@ -4538,7 +4538,7 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>99</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="O22">
         <v>84.09999999999999</v>
@@ -4597,16 +4597,16 @@
         <v>87.5</v>
       </c>
       <c r="N23">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="O23">
         <v>77.3</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="Q23">
-        <v>98.5</v>
+        <v>79.8</v>
       </c>
       <c r="R23">
         <v>56.3</v>
@@ -4656,16 +4656,16 @@
         <v>100</v>
       </c>
       <c r="N24">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="O24">
+        <v>100</v>
+      </c>
+      <c r="P24">
+        <v>100</v>
+      </c>
+      <c r="Q24">
         <v>98</v>
-      </c>
-      <c r="O24">
-        <v>100</v>
-      </c>
-      <c r="P24">
-        <v>100</v>
-      </c>
-      <c r="Q24">
-        <v>97</v>
       </c>
       <c r="R24">
         <v>95.3</v>
@@ -4724,7 +4724,7 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="R25">
         <v>95.3</v>
@@ -4842,7 +4842,7 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -4892,7 +4892,7 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="O28">
         <v>88.59999999999999</v>
@@ -5019,7 +5019,7 @@
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="R30">
         <v>100</v>
@@ -5069,7 +5069,7 @@
         <v>92.5</v>
       </c>
       <c r="N31">
-        <v>98</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="O31">
         <v>77.3</v>
@@ -5078,7 +5078,7 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="R31">
         <v>93.8</v>
@@ -5128,16 +5128,16 @@
         <v>90</v>
       </c>
       <c r="N32">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="O32">
         <v>77.3</v>
       </c>
       <c r="P32">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="Q32">
-        <v>95.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="R32">
         <v>85.90000000000001</v>
@@ -5187,16 +5187,16 @@
         <v>85</v>
       </c>
       <c r="N33">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="O33">
         <v>70.5</v>
       </c>
       <c r="P33">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="Q33">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="R33">
         <v>54.7</v>
@@ -5246,7 +5246,7 @@
         <v>92.5</v>
       </c>
       <c r="N34">
-        <v>98</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="O34">
         <v>77.3</v>
@@ -5255,7 +5255,7 @@
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="R34">
         <v>98.40000000000001</v>
@@ -5305,7 +5305,7 @@
         <v>95</v>
       </c>
       <c r="N35">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="O35">
         <v>84.09999999999999</v>
@@ -5364,7 +5364,7 @@
         <v>100</v>
       </c>
       <c r="N36">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O36">
         <v>90.90000000000001</v>
@@ -5500,7 +5500,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -5509,19 +5509,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>84.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>15.2</v>
+        <v>6.1</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5532,7 +5532,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -5553,7 +5553,7 @@
         <v>6.1</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5564,7 +5564,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
@@ -5585,7 +5585,7 @@
         <v>3</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5599,7 +5599,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C7">
         <v>33</v>
@@ -5617,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5667,7 +5667,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5705,7 +5705,7 @@
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
         <v>83</v>
@@ -5728,7 +5728,7 @@
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
         <v>83</v>
@@ -5751,7 +5751,7 @@
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
         <v>84</v>
@@ -5774,7 +5774,7 @@
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
         <v>84</v>
@@ -5791,13 +5791,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920312</v>
+        <v>22330051920408</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
         <v>85</v>
@@ -5814,22 +5814,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920312</v>
+        <v>22330051920408</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
         <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5837,13 +5837,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920397</v>
+        <v>22330051920291</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
         <v>86</v>
@@ -5860,22 +5860,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920397</v>
+        <v>22330051920294</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920291</v>
+        <v>22330051920303</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
         <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5906,16 +5906,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920294</v>
+        <v>22330051920307</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920303</v>
+        <v>22330051920312</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5952,22 +5952,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920417</v>
+        <v>22330051920370</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5975,16 +5975,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920307</v>
+        <v>22330051920397</v>
       </c>
       <c r="B14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" t="s">
         <v>74</v>
       </c>
-      <c r="C14" t="s">
-        <v>81</v>
-      </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -5998,16 +5998,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920370</v>
+        <v>22330051920314</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
@@ -6016,29 +6016,6 @@
         <v>57</v>
       </c>
       <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920314</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" t="s">
-        <v>93</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ASV - Estadisticos 20222.xlsx
+++ b/grupos/2ASV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
   <si>
     <t>Materia</t>
   </si>
@@ -194,12 +194,12 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Saucedo Rivalcoba Graciela</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Saucedo Rivalcoba Graciela</t>
-  </si>
-  <si>
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
@@ -218,85 +218,79 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>PANTOJA</t>
   </si>
   <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CESAR</t>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>OLGUIN</t>
   </si>
   <si>
     <t>TELLEZ</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
+    <t>LUIS GUSTAVO</t>
+  </si>
+  <si>
     <t>ABDIEL ARMANDO</t>
   </si>
   <si>
+    <t>JOSUE ISRAEL</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
+    <t>JARED DE JESUS</t>
+  </si>
+  <si>
+    <t>MIRIAM AIMAR</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
     <t>DIEGO</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>LUIS GUSTAVO</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>MIRIAM AIMAR</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
   </si>
   <si>
     <t>GUILLERMO ALEXANDER</t>
@@ -840,7 +834,7 @@
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -917,7 +911,7 @@
         <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -935,7 +929,7 @@
         <v>6</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -994,7 +988,7 @@
         <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1071,7 +1065,7 @@
         <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1148,7 +1142,7 @@
         <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -1225,7 +1219,7 @@
         <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1243,7 +1237,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1302,7 +1296,7 @@
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1379,7 +1373,7 @@
         <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>7</v>
@@ -1456,7 +1450,7 @@
         <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>9</v>
@@ -1474,7 +1468,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1533,7 +1527,7 @@
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1610,7 +1604,7 @@
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1687,7 +1681,7 @@
         <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1764,7 +1758,7 @@
         <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>6</v>
@@ -1782,7 +1776,7 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1841,7 +1835,7 @@
         <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -1859,7 +1853,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1918,7 +1912,7 @@
         <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -1995,7 +1989,7 @@
         <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -2072,7 +2066,7 @@
         <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>8</v>
@@ -2149,7 +2143,7 @@
         <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2226,7 +2220,7 @@
         <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>7</v>
@@ -2303,7 +2297,7 @@
         <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>5</v>
@@ -2380,7 +2374,7 @@
         <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>7</v>
@@ -2398,7 +2392,7 @@
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2457,7 +2451,7 @@
         <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2475,7 +2469,7 @@
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2534,7 +2528,7 @@
         <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2611,7 +2605,7 @@
         <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -2688,7 +2682,7 @@
         <v>6</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>8</v>
@@ -2706,7 +2700,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2765,7 +2759,7 @@
         <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -2842,7 +2836,7 @@
         <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -2919,7 +2913,7 @@
         <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>7</v>
@@ -2937,7 +2931,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2996,7 +2990,7 @@
         <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>6</v>
@@ -3014,7 +3008,7 @@
         <v>6</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3073,7 +3067,7 @@
         <v>5</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
         <v>5</v>
@@ -3150,7 +3144,7 @@
         <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
         <v>7</v>
@@ -3168,7 +3162,7 @@
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3227,7 +3221,7 @@
         <v>7</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T35">
         <v>7</v>
@@ -3304,7 +3298,7 @@
         <v>8</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T36">
         <v>8</v>
@@ -3322,7 +3316,7 @@
         <v>8</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3491,7 +3485,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3550,7 +3544,7 @@
         <v>92.2</v>
       </c>
       <c r="S5">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3727,7 +3721,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S8">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4081,7 +4075,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="S14">
-        <v>95</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4199,7 +4193,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S16">
-        <v>87.5</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4258,7 +4252,7 @@
         <v>92.2</v>
       </c>
       <c r="S17">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4435,7 +4429,7 @@
         <v>95.3</v>
       </c>
       <c r="S20">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4612,7 +4606,7 @@
         <v>56.3</v>
       </c>
       <c r="S23">
-        <v>87.5</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5084,7 +5078,7 @@
         <v>93.8</v>
       </c>
       <c r="S31">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5143,7 +5137,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="S32">
-        <v>90</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5202,7 +5196,7 @@
         <v>54.7</v>
       </c>
       <c r="S33">
-        <v>85</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5261,7 +5255,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="S34">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5320,7 +5314,7 @@
         <v>92.2</v>
       </c>
       <c r="S35">
-        <v>95</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5468,7 +5462,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -5477,19 +5471,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>81.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>18.2</v>
+        <v>6.1</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5500,7 +5494,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -5521,7 +5515,7 @@
         <v>6.1</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5667,7 +5661,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5699,16 +5693,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920302</v>
+        <v>22330051920291</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5722,22 +5716,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920302</v>
+        <v>22330051920294</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
         <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5745,13 +5739,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920308</v>
+        <v>22330051920302</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
         <v>84</v>
@@ -5768,22 +5762,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920308</v>
+        <v>22330051920307</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5791,16 +5785,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920408</v>
+        <v>22330051920308</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
         <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5814,22 +5808,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920408</v>
+        <v>22330051920312</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5837,16 +5831,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920291</v>
+        <v>22330051920370</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5860,16 +5854,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920294</v>
+        <v>22330051920397</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -5883,22 +5877,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920303</v>
+        <v>22330051920408</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5906,16 +5900,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920307</v>
+        <v>22330051920314</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -5924,98 +5918,6 @@
         <v>57</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920312</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920370</v>
-      </c>
-      <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920397</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920314</v>
-      </c>
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ASV - Estadisticos 20222.xlsx
+++ b/grupos/2ASV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="74">
   <si>
     <t>Materia</t>
   </si>
@@ -218,76 +218,22 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
     <t>TELLEZ</t>
   </si>
   <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>LUIS GUSTAVO</t>
-  </si>
-  <si>
     <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>MIRIAM AIMAR</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
   </si>
   <si>
     <t>DIEGO</t>
@@ -822,7 +768,7 @@
         <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
         <v>7</v>
@@ -899,7 +845,7 @@
         <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>6</v>
@@ -917,7 +863,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>6</v>
@@ -976,7 +922,7 @@
         <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
         <v>7</v>
@@ -1053,7 +999,7 @@
         <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>8</v>
@@ -1071,7 +1017,7 @@
         <v>8</v>
       </c>
       <c r="U7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1130,7 +1076,7 @@
         <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>8</v>
@@ -1207,7 +1153,7 @@
         <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>8</v>
@@ -1284,7 +1230,7 @@
         <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
         <v>8</v>
@@ -1361,7 +1307,7 @@
         <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>8</v>
@@ -1379,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1438,7 +1384,7 @@
         <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
         <v>6</v>
@@ -1515,7 +1461,7 @@
         <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>8</v>
@@ -1592,7 +1538,7 @@
         <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>7</v>
@@ -1669,7 +1615,7 @@
         <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>7</v>
@@ -1746,7 +1692,7 @@
         <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
         <v>6</v>
@@ -1823,7 +1769,7 @@
         <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
         <v>7</v>
@@ -1900,7 +1846,7 @@
         <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>7</v>
@@ -1977,7 +1923,7 @@
         <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
         <v>7</v>
@@ -1995,7 +1941,7 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>7</v>
@@ -2054,7 +2000,7 @@
         <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>7</v>
@@ -2131,7 +2077,7 @@
         <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>7</v>
@@ -2208,7 +2154,7 @@
         <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>7</v>
@@ -2226,7 +2172,7 @@
         <v>7</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>7</v>
@@ -2285,7 +2231,7 @@
         <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>5</v>
@@ -2362,7 +2308,7 @@
         <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>8</v>
@@ -2380,7 +2326,7 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -2439,7 +2385,7 @@
         <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>7</v>
@@ -2516,7 +2462,7 @@
         <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>9</v>
@@ -2534,7 +2480,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -2593,7 +2539,7 @@
         <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>7</v>
@@ -2670,7 +2616,7 @@
         <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
         <v>7</v>
@@ -2688,7 +2634,7 @@
         <v>8</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>7</v>
@@ -2747,7 +2693,7 @@
         <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>9</v>
@@ -2824,7 +2770,7 @@
         <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>7</v>
@@ -2901,7 +2847,7 @@
         <v>7</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>8</v>
@@ -2919,7 +2865,7 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -2978,7 +2924,7 @@
         <v>7</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
         <v>5</v>
@@ -3055,7 +3001,7 @@
         <v>5</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>5</v>
@@ -3132,7 +3078,7 @@
         <v>7</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
         <v>7</v>
@@ -3150,7 +3096,7 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>8</v>
@@ -3209,7 +3155,7 @@
         <v>7</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P35">
         <v>7</v>
@@ -3286,7 +3232,7 @@
         <v>8</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
         <v>8</v>
@@ -3473,7 +3419,7 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -3532,7 +3478,7 @@
         <v>97.5</v>
       </c>
       <c r="O5">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3650,7 +3596,7 @@
         <v>98.8</v>
       </c>
       <c r="O7">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -3709,7 +3655,7 @@
         <v>98.8</v>
       </c>
       <c r="O8">
-        <v>84.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -3886,7 +3832,7 @@
         <v>96.3</v>
       </c>
       <c r="O11">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -3945,7 +3891,7 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -4004,7 +3950,7 @@
         <v>98.8</v>
       </c>
       <c r="O13">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -4063,7 +4009,7 @@
         <v>99.40000000000001</v>
       </c>
       <c r="O14">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -4181,7 +4127,7 @@
         <v>96.3</v>
       </c>
       <c r="O16">
-        <v>68.2</v>
+        <v>46.9</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4240,7 +4186,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="O17">
-        <v>88.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -4299,7 +4245,7 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P18">
         <v>100</v>
@@ -4417,7 +4363,7 @@
         <v>99.40000000000001</v>
       </c>
       <c r="O20">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -4535,7 +4481,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="O22">
-        <v>84.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -4594,7 +4540,7 @@
         <v>60</v>
       </c>
       <c r="O23">
-        <v>77.3</v>
+        <v>53.1</v>
       </c>
       <c r="P23">
         <v>86.7</v>
@@ -4712,7 +4658,7 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -4889,7 +4835,7 @@
         <v>98.8</v>
       </c>
       <c r="O28">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -5066,7 +5012,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="O31">
-        <v>77.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P31">
         <v>100</v>
@@ -5125,7 +5071,7 @@
         <v>93.8</v>
       </c>
       <c r="O32">
-        <v>77.3</v>
+        <v>53.1</v>
       </c>
       <c r="P32">
         <v>86.7</v>
@@ -5184,7 +5130,7 @@
         <v>60</v>
       </c>
       <c r="O33">
-        <v>70.5</v>
+        <v>48.4</v>
       </c>
       <c r="P33">
         <v>86.7</v>
@@ -5243,7 +5189,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="O34">
-        <v>77.3</v>
+        <v>82.8</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -5302,7 +5248,7 @@
         <v>97.5</v>
       </c>
       <c r="O35">
-        <v>84.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="P35">
         <v>100</v>
@@ -5361,7 +5307,7 @@
         <v>99.40000000000001</v>
       </c>
       <c r="O36">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P36">
         <v>100</v>
@@ -5439,19 +5385,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>63.6</v>
+        <v>84.8</v>
       </c>
       <c r="G2" s="2">
-        <v>36.4</v>
+        <v>15.2</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5661,7 +5607,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5693,16 +5639,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920291</v>
+        <v>22330051920302</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5716,16 +5662,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920294</v>
+        <v>22330051920408</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -5739,16 +5685,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920302</v>
+        <v>22330051920314</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5757,167 +5703,6 @@
         <v>57</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920307</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920308</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920312</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920370</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920397</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920408</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920314</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>
